--- a/excel-files/PASIG/DELA PAZ HIGH SCHOOL.xlsx
+++ b/excel-files/PASIG/DELA PAZ HIGH SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29728"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29922"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="160" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FA2B72F-1AC4-42EE-A679-7B32F3E83E18}"/>
+  <xr:revisionPtr revIDLastSave="610" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26280500-2D74-4284-97A3-ACF94B747921}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="92">
   <si>
     <t>Grade Level</t>
   </si>
@@ -229,6 +229,9 @@
     <t>MAPEH</t>
   </si>
   <si>
+    <t>RO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Quantity based on Target ADM-SLM - Q1 </t>
   </si>
   <si>
@@ -311,9 +314,6 @@
   </si>
   <si>
     <t>Arts</t>
-  </si>
-  <si>
-    <t>RO</t>
   </si>
 </sst>
 </file>
@@ -742,6 +742,12 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -753,12 +759,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4424,7 +4424,9 @@
       <c r="B51" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C51" s="10"/>
+      <c r="C51" s="10">
+        <v>202</v>
+      </c>
       <c r="D51" s="10">
         <v>240</v>
       </c>
@@ -4440,7 +4442,7 @@
       </c>
       <c r="H51" s="4">
         <f t="shared" ref="H51:H59" si="11">IF((D51-C51)&lt;0,0,D51-C51)</f>
-        <v>240</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="27.75" customHeight="1">
@@ -4450,13 +4452,17 @@
       <c r="B52" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C52" s="10"/>
-      <c r="D52" s="10"/>
+      <c r="C52" s="10">
+        <v>202</v>
+      </c>
+      <c r="D52" s="10">
+        <v>0</v>
+      </c>
       <c r="E52" s="10"/>
       <c r="F52" s="12"/>
       <c r="G52" s="3">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="H52" s="4">
         <f t="shared" si="11"/>
@@ -4470,7 +4476,9 @@
       <c r="B53" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C53" s="10"/>
+      <c r="C53" s="10">
+        <v>202</v>
+      </c>
       <c r="D53" s="10">
         <v>240</v>
       </c>
@@ -4486,7 +4494,7 @@
       </c>
       <c r="H53" s="4">
         <f t="shared" si="11"/>
-        <v>240</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="27.75" customHeight="1">
@@ -4496,7 +4504,9 @@
       <c r="B54" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C54" s="10"/>
+      <c r="C54" s="10">
+        <v>202</v>
+      </c>
       <c r="D54" s="10">
         <v>240</v>
       </c>
@@ -4510,7 +4520,7 @@
       </c>
       <c r="H54" s="4">
         <f t="shared" si="11"/>
-        <v>240</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="39" customHeight="1">
@@ -4520,7 +4530,9 @@
       <c r="B55" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C55" s="10"/>
+      <c r="C55" s="10">
+        <v>202</v>
+      </c>
       <c r="D55" s="10">
         <v>240</v>
       </c>
@@ -4536,7 +4548,7 @@
       </c>
       <c r="H55" s="4">
         <f t="shared" si="11"/>
-        <v>240</v>
+        <v>38</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="27.75" customHeight="1">
@@ -4546,7 +4558,9 @@
       <c r="B56" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C56" s="10"/>
+      <c r="C56" s="10">
+        <v>202</v>
+      </c>
       <c r="D56" s="10">
         <v>240</v>
       </c>
@@ -4562,7 +4576,7 @@
       </c>
       <c r="H56" s="4">
         <f t="shared" si="11"/>
-        <v>240</v>
+        <v>38</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="27.75" customHeight="1">
@@ -4572,7 +4586,9 @@
       <c r="B57" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C57" s="10"/>
+      <c r="C57" s="10">
+        <v>202</v>
+      </c>
       <c r="D57" s="10">
         <v>240</v>
       </c>
@@ -4588,7 +4604,7 @@
       </c>
       <c r="H57" s="4">
         <f t="shared" si="11"/>
-        <v>240</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="27.75" customHeight="1">
@@ -4598,7 +4614,9 @@
       <c r="B58" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C58" s="10"/>
+      <c r="C58" s="10">
+        <v>202</v>
+      </c>
       <c r="D58" s="10">
         <v>240</v>
       </c>
@@ -4612,7 +4630,7 @@
       </c>
       <c r="H58" s="4">
         <f t="shared" si="11"/>
-        <v>240</v>
+        <v>38</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="27.75" customHeight="1">
@@ -4622,7 +4640,9 @@
       <c r="B59" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C59" s="10"/>
+      <c r="C59" s="10">
+        <v>202</v>
+      </c>
       <c r="D59" s="10">
         <v>240</v>
       </c>
@@ -4638,7 +4658,7 @@
       </c>
       <c r="H59" s="4">
         <f t="shared" si="11"/>
-        <v>240</v>
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="27.75" customHeight="1">
@@ -4658,13 +4678,17 @@
       <c r="B61" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C61" s="10"/>
-      <c r="D61" s="10"/>
+      <c r="C61" s="10">
+        <v>173</v>
+      </c>
+      <c r="D61" s="10">
+        <v>0</v>
+      </c>
       <c r="E61" s="10"/>
       <c r="F61" s="12"/>
       <c r="G61" s="3">
         <f t="shared" ref="G61:G69" si="12">IF((C61-D61)&lt;0,0,C61-D61)</f>
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="H61" s="4">
         <f t="shared" ref="H61:H69" si="13">IF((D61-C61)&lt;0,0,D61-C61)</f>
@@ -4678,13 +4702,17 @@
       <c r="B62" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C62" s="10"/>
-      <c r="D62" s="10"/>
+      <c r="C62" s="10">
+        <v>173</v>
+      </c>
+      <c r="D62" s="10">
+        <v>0</v>
+      </c>
       <c r="E62" s="10"/>
       <c r="F62" s="12"/>
       <c r="G62" s="3">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="H62" s="4">
         <f t="shared" si="13"/>
@@ -4698,7 +4726,9 @@
       <c r="B63" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C63" s="10"/>
+      <c r="C63" s="10">
+        <v>173</v>
+      </c>
       <c r="D63" s="10">
         <v>149</v>
       </c>
@@ -4710,11 +4740,11 @@
       </c>
       <c r="G63" s="3">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H63" s="4">
         <f t="shared" si="13"/>
-        <v>149</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="27.75" customHeight="1">
@@ -4724,7 +4754,9 @@
       <c r="B64" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C64" s="10"/>
+      <c r="C64" s="10">
+        <v>173</v>
+      </c>
       <c r="D64" s="10">
         <v>149</v>
       </c>
@@ -4736,11 +4768,11 @@
       </c>
       <c r="G64" s="3">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H64" s="4">
         <f t="shared" si="13"/>
-        <v>149</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="27.75" customHeight="1">
@@ -4750,13 +4782,17 @@
       <c r="B65" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C65" s="10"/>
-      <c r="D65" s="10"/>
+      <c r="C65" s="10">
+        <v>173</v>
+      </c>
+      <c r="D65" s="10">
+        <v>0</v>
+      </c>
       <c r="E65" s="10"/>
       <c r="F65" s="12"/>
       <c r="G65" s="3">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="H65" s="4">
         <f t="shared" si="13"/>
@@ -4770,7 +4806,9 @@
       <c r="B66" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C66" s="10"/>
+      <c r="C66" s="10">
+        <v>173</v>
+      </c>
       <c r="D66" s="10">
         <v>149</v>
       </c>
@@ -4780,11 +4818,11 @@
       </c>
       <c r="G66" s="3">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H66" s="4">
         <f t="shared" si="13"/>
-        <v>149</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="27.75" customHeight="1">
@@ -4794,13 +4832,17 @@
       <c r="B67" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C67" s="10"/>
-      <c r="D67" s="10"/>
+      <c r="C67" s="10">
+        <v>173</v>
+      </c>
+      <c r="D67" s="10">
+        <v>0</v>
+      </c>
       <c r="E67" s="10"/>
       <c r="F67" s="12"/>
       <c r="G67" s="3">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="H67" s="4">
         <f t="shared" si="13"/>
@@ -4814,13 +4856,17 @@
       <c r="B68" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C68" s="10"/>
-      <c r="D68" s="10"/>
+      <c r="C68" s="10">
+        <v>173</v>
+      </c>
+      <c r="D68" s="10">
+        <v>0</v>
+      </c>
       <c r="E68" s="10"/>
       <c r="F68" s="12"/>
       <c r="G68" s="3">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="H68" s="4">
         <f t="shared" si="13"/>
@@ -4834,13 +4880,17 @@
       <c r="B69" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C69" s="10"/>
-      <c r="D69" s="10"/>
+      <c r="C69" s="10">
+        <v>173</v>
+      </c>
+      <c r="D69" s="10">
+        <v>0</v>
+      </c>
       <c r="E69" s="10"/>
       <c r="F69" s="12"/>
       <c r="G69" s="3">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="H69" s="4">
         <f t="shared" si="13"/>
@@ -4864,13 +4914,17 @@
       <c r="B71" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C71" s="10"/>
-      <c r="D71" s="10"/>
+      <c r="C71" s="10">
+        <v>169</v>
+      </c>
+      <c r="D71" s="10">
+        <v>0</v>
+      </c>
       <c r="E71" s="10"/>
       <c r="F71" s="12"/>
       <c r="G71" s="3">
         <f t="shared" ref="G71:G79" si="14">IF((C71-D71)&lt;0,0,C71-D71)</f>
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="H71" s="4">
         <f t="shared" ref="H71:H79" si="15">IF((D71-C71)&lt;0,0,D71-C71)</f>
@@ -4884,7 +4938,9 @@
       <c r="B72" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C72" s="10"/>
+      <c r="C72" s="10">
+        <v>169</v>
+      </c>
       <c r="D72" s="10">
         <v>236</v>
       </c>
@@ -4900,7 +4956,7 @@
       </c>
       <c r="H72" s="4">
         <f t="shared" si="15"/>
-        <v>236</v>
+        <v>67</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="27.75" customHeight="1">
@@ -4910,13 +4966,17 @@
       <c r="B73" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C73" s="10"/>
-      <c r="D73" s="10"/>
+      <c r="C73" s="10">
+        <v>169</v>
+      </c>
+      <c r="D73" s="10">
+        <v>0</v>
+      </c>
       <c r="E73" s="10"/>
       <c r="F73" s="12"/>
       <c r="G73" s="3">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="H73" s="4">
         <f t="shared" si="15"/>
@@ -4930,13 +4990,17 @@
       <c r="B74" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C74" s="10"/>
-      <c r="D74" s="10"/>
+      <c r="C74" s="10">
+        <v>169</v>
+      </c>
+      <c r="D74" s="10">
+        <v>0</v>
+      </c>
       <c r="E74" s="10"/>
       <c r="F74" s="12"/>
       <c r="G74" s="3">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="H74" s="4">
         <f t="shared" si="15"/>
@@ -4950,13 +5014,17 @@
       <c r="B75" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C75" s="10"/>
-      <c r="D75" s="10"/>
+      <c r="C75" s="10">
+        <v>169</v>
+      </c>
+      <c r="D75" s="10">
+        <v>0</v>
+      </c>
       <c r="E75" s="10"/>
       <c r="F75" s="12"/>
       <c r="G75" s="3">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="H75" s="4">
         <f t="shared" si="15"/>
@@ -4970,13 +5038,17 @@
       <c r="B76" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C76" s="10"/>
-      <c r="D76" s="10"/>
+      <c r="C76" s="10">
+        <v>169</v>
+      </c>
+      <c r="D76" s="10">
+        <v>0</v>
+      </c>
       <c r="E76" s="10"/>
       <c r="F76" s="12"/>
       <c r="G76" s="3">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="H76" s="4">
         <f t="shared" si="15"/>
@@ -4990,13 +5062,17 @@
       <c r="B77" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C77" s="10"/>
-      <c r="D77" s="10"/>
+      <c r="C77" s="10">
+        <v>169</v>
+      </c>
+      <c r="D77" s="10">
+        <v>0</v>
+      </c>
       <c r="E77" s="10"/>
       <c r="F77" s="12"/>
       <c r="G77" s="3">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="H77" s="4">
         <f t="shared" si="15"/>
@@ -5010,13 +5086,17 @@
       <c r="B78" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C78" s="10"/>
-      <c r="D78" s="10"/>
+      <c r="C78" s="10">
+        <v>169</v>
+      </c>
+      <c r="D78" s="10">
+        <v>0</v>
+      </c>
       <c r="E78" s="10"/>
       <c r="F78" s="12"/>
       <c r="G78" s="3">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="H78" s="4">
         <f t="shared" si="15"/>
@@ -5030,13 +5110,17 @@
       <c r="B79" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C79" s="10"/>
-      <c r="D79" s="10"/>
+      <c r="C79" s="10">
+        <v>169</v>
+      </c>
+      <c r="D79" s="10">
+        <v>0</v>
+      </c>
       <c r="E79" s="10"/>
       <c r="F79" s="12"/>
       <c r="G79" s="3">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="H79" s="4">
         <f t="shared" si="15"/>
@@ -5060,13 +5144,17 @@
       <c r="B81" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C81" s="10"/>
-      <c r="D81" s="10"/>
+      <c r="C81" s="10">
+        <v>130</v>
+      </c>
+      <c r="D81" s="10">
+        <v>0</v>
+      </c>
       <c r="E81" s="10"/>
       <c r="F81" s="12"/>
       <c r="G81" s="3">
         <f t="shared" ref="G81:G89" si="16">IF((C81-D81)&lt;0,0,C81-D81)</f>
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="H81" s="4">
         <f t="shared" ref="H81:H89" si="17">IF((D81-C81)&lt;0,0,D81-C81)</f>
@@ -5080,7 +5168,9 @@
       <c r="B82" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C82" s="10"/>
+      <c r="C82" s="10">
+        <v>130</v>
+      </c>
       <c r="D82" s="10">
         <v>211</v>
       </c>
@@ -5096,7 +5186,7 @@
       </c>
       <c r="H82" s="4">
         <f t="shared" si="17"/>
-        <v>211</v>
+        <v>81</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="27.75" customHeight="1">
@@ -5106,13 +5196,17 @@
       <c r="B83" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C83" s="10"/>
-      <c r="D83" s="10"/>
+      <c r="C83" s="10">
+        <v>130</v>
+      </c>
+      <c r="D83" s="10">
+        <v>0</v>
+      </c>
       <c r="E83" s="10"/>
       <c r="F83" s="12"/>
       <c r="G83" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="H83" s="4">
         <f t="shared" si="17"/>
@@ -5126,13 +5220,17 @@
       <c r="B84" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C84" s="10"/>
-      <c r="D84" s="10"/>
+      <c r="C84" s="10">
+        <v>130</v>
+      </c>
+      <c r="D84" s="10">
+        <v>0</v>
+      </c>
       <c r="E84" s="10"/>
       <c r="F84" s="12"/>
       <c r="G84" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="H84" s="4">
         <f t="shared" si="17"/>
@@ -5146,13 +5244,17 @@
       <c r="B85" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C85" s="10"/>
-      <c r="D85" s="10"/>
+      <c r="C85" s="10">
+        <v>130</v>
+      </c>
+      <c r="D85" s="10">
+        <v>0</v>
+      </c>
       <c r="E85" s="10"/>
       <c r="F85" s="12"/>
       <c r="G85" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="H85" s="4">
         <f t="shared" si="17"/>
@@ -5166,13 +5268,17 @@
       <c r="B86" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C86" s="10"/>
-      <c r="D86" s="10"/>
+      <c r="C86" s="10">
+        <v>130</v>
+      </c>
+      <c r="D86" s="10">
+        <v>0</v>
+      </c>
       <c r="E86" s="10"/>
       <c r="F86" s="12"/>
       <c r="G86" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="H86" s="4">
         <f t="shared" si="17"/>
@@ -5186,13 +5292,17 @@
       <c r="B87" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C87" s="10"/>
-      <c r="D87" s="10"/>
+      <c r="C87" s="10">
+        <v>130</v>
+      </c>
+      <c r="D87" s="10">
+        <v>0</v>
+      </c>
       <c r="E87" s="10"/>
       <c r="F87" s="12"/>
       <c r="G87" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="H87" s="4">
         <f t="shared" si="17"/>
@@ -5206,13 +5316,17 @@
       <c r="B88" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C88" s="10"/>
-      <c r="D88" s="10"/>
+      <c r="C88" s="10">
+        <v>130</v>
+      </c>
+      <c r="D88" s="10">
+        <v>0</v>
+      </c>
       <c r="E88" s="10"/>
       <c r="F88" s="12"/>
       <c r="G88" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="H88" s="4">
         <f t="shared" si="17"/>
@@ -5226,13 +5340,17 @@
       <c r="B89" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C89" s="10"/>
-      <c r="D89" s="10"/>
+      <c r="C89" s="10">
+        <v>130</v>
+      </c>
+      <c r="D89" s="10">
+        <v>0</v>
+      </c>
       <c r="E89" s="10"/>
       <c r="F89" s="12"/>
       <c r="G89" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="H89" s="4">
         <f t="shared" si="17"/>
@@ -5415,12 +5533,15 @@
     <protectedRange sqref="F1:F98" name="SOURCE"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6 E8:E12 E14:E19 E21:E29 E31:E39 E41:E49 E51:E59 E61:E69 E71:E79 E81:E89" xr:uid="{0499A7B6-8E14-4B6D-8A7A-F50EAA8D9572}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5432,7 +5553,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5462,38 +5583,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -5532,10 +5653,10 @@
       <c r="L2" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M2" s="44" t="s">
+      <c r="M2" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="40" t="s">
         <v>47</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -5568,10 +5689,10 @@
       <c r="X2" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="Y2" s="45" t="s">
+      <c r="Y2" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="Z2" s="45" t="s">
+      <c r="Z2" s="41" t="s">
         <v>59</v>
       </c>
       <c r="AA2" s="26" t="s">
@@ -9328,24 +9449,28 @@
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="19.5">
       <c r="A63" s="10">
         <v>7</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C63" s="10"/>
+      <c r="C63" s="10">
+        <v>202</v>
+      </c>
       <c r="D63" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E63" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="E63" s="12">
+        <v>0</v>
+      </c>
       <c r="F63" s="10"/>
       <c r="G63" s="12"/>
       <c r="H63" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="I63" s="12">
         <f t="shared" si="3"/>
@@ -9353,14 +9478,16 @@
       </c>
       <c r="J63" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K63" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="K63" s="12">
+        <v>0</v>
+      </c>
       <c r="L63" s="10"/>
       <c r="M63" s="12"/>
       <c r="N63" s="12">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="O63" s="12">
         <f t="shared" si="11"/>
@@ -9368,14 +9495,16 @@
       </c>
       <c r="P63" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q63" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="Q63" s="12">
+        <v>0</v>
+      </c>
       <c r="R63" s="10"/>
       <c r="S63" s="12"/>
       <c r="T63" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="U63" s="12">
         <f t="shared" si="13"/>
@@ -9383,38 +9512,46 @@
       </c>
       <c r="V63" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W63" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="W63" s="12">
+        <v>82</v>
+      </c>
       <c r="X63" s="10"/>
-      <c r="Y63" s="12"/>
+      <c r="Y63" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="Z63" s="12">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1534</v>
       </c>
       <c r="AA63" s="12">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="10">
         <v>7</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C64" s="10"/>
+      <c r="C64" s="10">
+        <v>202</v>
+      </c>
       <c r="D64" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E64" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="E64" s="12">
+        <v>0</v>
+      </c>
       <c r="F64" s="10"/>
       <c r="G64" s="12"/>
       <c r="H64" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="I64" s="12">
         <f t="shared" si="3"/>
@@ -9422,14 +9559,16 @@
       </c>
       <c r="J64" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K64" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="K64" s="12">
+        <v>0</v>
+      </c>
       <c r="L64" s="10"/>
       <c r="M64" s="12"/>
       <c r="N64" s="12">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="O64" s="12">
         <f t="shared" si="11"/>
@@ -9437,14 +9576,16 @@
       </c>
       <c r="P64" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q64" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="Q64" s="12">
+        <v>0</v>
+      </c>
       <c r="R64" s="10"/>
       <c r="S64" s="12"/>
       <c r="T64" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="U64" s="12">
         <f t="shared" si="13"/>
@@ -9452,38 +9593,46 @@
       </c>
       <c r="V64" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W64" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="W64" s="12">
+        <v>82</v>
+      </c>
       <c r="X64" s="10"/>
-      <c r="Y64" s="12"/>
+      <c r="Y64" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="Z64" s="12">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1534</v>
       </c>
       <c r="AA64" s="12">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="10">
         <v>7</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C65" s="10"/>
+      <c r="C65" s="10">
+        <v>202</v>
+      </c>
       <c r="D65" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E65" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="E65" s="12">
+        <v>0</v>
+      </c>
       <c r="F65" s="10"/>
       <c r="G65" s="12"/>
       <c r="H65" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="I65" s="12">
         <f t="shared" si="3"/>
@@ -9491,14 +9640,16 @@
       </c>
       <c r="J65" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K65" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="K65" s="12">
+        <v>0</v>
+      </c>
       <c r="L65" s="10"/>
       <c r="M65" s="12"/>
       <c r="N65" s="12">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="O65" s="12">
         <f t="shared" si="11"/>
@@ -9506,14 +9657,16 @@
       </c>
       <c r="P65" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q65" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="Q65" s="12">
+        <v>0</v>
+      </c>
       <c r="R65" s="10"/>
       <c r="S65" s="12"/>
       <c r="T65" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="U65" s="12">
         <f t="shared" si="13"/>
@@ -9521,38 +9674,46 @@
       </c>
       <c r="V65" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W65" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="W65" s="12">
+        <v>82</v>
+      </c>
       <c r="X65" s="10"/>
-      <c r="Y65" s="12"/>
+      <c r="Y65" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="Z65" s="12">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1534</v>
       </c>
       <c r="AA65" s="12">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" ht="19.5">
       <c r="A66" s="10">
         <v>7</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C66" s="10"/>
+      <c r="C66" s="10">
+        <v>202</v>
+      </c>
       <c r="D66" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E66" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="E66" s="12">
+        <v>0</v>
+      </c>
       <c r="F66" s="10"/>
       <c r="G66" s="12"/>
       <c r="H66" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="I66" s="12">
         <f t="shared" si="3"/>
@@ -9560,14 +9721,16 @@
       </c>
       <c r="J66" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K66" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="K66" s="12">
+        <v>0</v>
+      </c>
       <c r="L66" s="10"/>
       <c r="M66" s="12"/>
       <c r="N66" s="12">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="O66" s="12">
         <f t="shared" si="11"/>
@@ -9575,14 +9738,16 @@
       </c>
       <c r="P66" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q66" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="Q66" s="12">
+        <v>0</v>
+      </c>
       <c r="R66" s="10"/>
       <c r="S66" s="12"/>
       <c r="T66" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="U66" s="12">
         <f t="shared" si="13"/>
@@ -9590,38 +9755,46 @@
       </c>
       <c r="V66" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W66" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="W66" s="12">
+        <v>82</v>
+      </c>
       <c r="X66" s="10"/>
-      <c r="Y66" s="12"/>
+      <c r="Y66" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="Z66" s="12">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1534</v>
       </c>
       <c r="AA66" s="12">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="38.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C67" s="10"/>
+      <c r="C67" s="10">
+        <v>202</v>
+      </c>
       <c r="D67" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E67" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="E67" s="12">
+        <v>0</v>
+      </c>
       <c r="F67" s="10"/>
       <c r="G67" s="12"/>
       <c r="H67" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="I67" s="12">
         <f t="shared" si="3"/>
@@ -9629,14 +9802,16 @@
       </c>
       <c r="J67" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K67" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="K67" s="12">
+        <v>0</v>
+      </c>
       <c r="L67" s="10"/>
       <c r="M67" s="12"/>
       <c r="N67" s="12">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="O67" s="12">
         <f t="shared" si="11"/>
@@ -9644,14 +9819,16 @@
       </c>
       <c r="P67" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q67" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="Q67" s="12">
+        <v>0</v>
+      </c>
       <c r="R67" s="10"/>
       <c r="S67" s="12"/>
       <c r="T67" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="U67" s="12">
         <f t="shared" si="13"/>
@@ -9659,38 +9836,46 @@
       </c>
       <c r="V67" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W67" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="W67" s="12">
+        <v>82</v>
+      </c>
       <c r="X67" s="10"/>
-      <c r="Y67" s="12"/>
+      <c r="Y67" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="Z67" s="12">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1534</v>
       </c>
       <c r="AA67" s="12">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C68" s="10"/>
+      <c r="C68" s="10">
+        <v>202</v>
+      </c>
       <c r="D68" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E68" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="E68" s="12">
+        <v>0</v>
+      </c>
       <c r="F68" s="10"/>
       <c r="G68" s="12"/>
       <c r="H68" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="I68" s="12">
         <f t="shared" si="3"/>
@@ -9698,14 +9883,16 @@
       </c>
       <c r="J68" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K68" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="K68" s="12">
+        <v>0</v>
+      </c>
       <c r="L68" s="10"/>
       <c r="M68" s="12"/>
       <c r="N68" s="12">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="O68" s="12">
         <f t="shared" si="11"/>
@@ -9713,14 +9900,16 @@
       </c>
       <c r="P68" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q68" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="Q68" s="12">
+        <v>0</v>
+      </c>
       <c r="R68" s="10"/>
       <c r="S68" s="12"/>
       <c r="T68" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="U68" s="12">
         <f t="shared" si="13"/>
@@ -9728,38 +9917,46 @@
       </c>
       <c r="V68" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W68" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="W68" s="12">
+        <v>82</v>
+      </c>
       <c r="X68" s="10"/>
-      <c r="Y68" s="12"/>
+      <c r="Y68" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="Z68" s="12">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1534</v>
       </c>
       <c r="AA68" s="12">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C69" s="10"/>
+      <c r="C69" s="10">
+        <v>202</v>
+      </c>
       <c r="D69" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E69" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="E69" s="12">
+        <v>0</v>
+      </c>
       <c r="F69" s="10"/>
       <c r="G69" s="12"/>
       <c r="H69" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="I69" s="12">
         <f t="shared" si="3"/>
@@ -9767,14 +9964,16 @@
       </c>
       <c r="J69" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K69" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="K69" s="12">
+        <v>0</v>
+      </c>
       <c r="L69" s="10"/>
       <c r="M69" s="12"/>
       <c r="N69" s="12">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="O69" s="12">
         <f t="shared" si="11"/>
@@ -9782,14 +9981,16 @@
       </c>
       <c r="P69" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q69" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="Q69" s="12">
+        <v>0</v>
+      </c>
       <c r="R69" s="10"/>
       <c r="S69" s="12"/>
       <c r="T69" s="12">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="U69" s="12">
         <f t="shared" si="13"/>
@@ -9797,38 +9998,46 @@
       </c>
       <c r="V69" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W69" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="W69" s="12">
+        <v>82</v>
+      </c>
       <c r="X69" s="10"/>
-      <c r="Y69" s="12"/>
+      <c r="Y69" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="Z69" s="12">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1534</v>
       </c>
       <c r="AA69" s="12">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C70" s="10"/>
+      <c r="C70" s="10">
+        <v>202</v>
+      </c>
       <c r="D70" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E70" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="E70" s="12">
+        <v>0</v>
+      </c>
       <c r="F70" s="10"/>
       <c r="G70" s="12"/>
       <c r="H70" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="I70" s="12">
         <f t="shared" si="3"/>
@@ -9836,14 +10045,16 @@
       </c>
       <c r="J70" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K70" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="K70" s="12">
+        <v>0</v>
+      </c>
       <c r="L70" s="10"/>
       <c r="M70" s="12"/>
       <c r="N70" s="12">
         <f t="shared" ref="N70:N126" si="16">IF((J70-K70)&lt;0,0,(J70-K70))</f>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="O70" s="12">
         <f t="shared" ref="O70:O126" si="17">IF((K70-J70)&lt;0,0,(K70-J70))</f>
@@ -9851,14 +10062,16 @@
       </c>
       <c r="P70" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q70" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="Q70" s="12">
+        <v>0</v>
+      </c>
       <c r="R70" s="10"/>
       <c r="S70" s="12"/>
       <c r="T70" s="12">
         <f t="shared" ref="T70:T127" si="18">IF((P70-Q70)&lt;0,0,(P70-Q70))</f>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="U70" s="12">
         <f t="shared" ref="U70:U127" si="19">IF((Q70-P70)&lt;0,0,(Q70-P70))</f>
@@ -9866,38 +10079,46 @@
       </c>
       <c r="V70" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W70" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="W70" s="12">
+        <v>82</v>
+      </c>
       <c r="X70" s="10"/>
-      <c r="Y70" s="12"/>
+      <c r="Y70" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="Z70" s="12">
         <f t="shared" ref="Z70:Z127" si="20">IF((V70-W70)&lt;0,0,(V70-W70))</f>
-        <v>0</v>
+        <v>1534</v>
       </c>
       <c r="AA70" s="12">
         <f t="shared" ref="AA70:AA127" si="21">IF((W70-V70)&lt;0,0,(W70-V70))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="19.5">
       <c r="A71" s="10">
         <v>7</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C71" s="10"/>
+      <c r="C71" s="10">
+        <v>202</v>
+      </c>
       <c r="D71" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E71" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="E71" s="12">
+        <v>0</v>
+      </c>
       <c r="F71" s="10"/>
       <c r="G71" s="12"/>
       <c r="H71" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="I71" s="12">
         <f t="shared" si="3"/>
@@ -9905,14 +10126,16 @@
       </c>
       <c r="J71" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K71" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="K71" s="12">
+        <v>0</v>
+      </c>
       <c r="L71" s="10"/>
       <c r="M71" s="12"/>
       <c r="N71" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="O71" s="12">
         <f t="shared" si="17"/>
@@ -9920,14 +10143,16 @@
       </c>
       <c r="P71" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q71" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="Q71" s="12">
+        <v>0</v>
+      </c>
       <c r="R71" s="10"/>
       <c r="S71" s="12"/>
       <c r="T71" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="U71" s="12">
         <f t="shared" si="19"/>
@@ -9935,14 +10160,18 @@
       </c>
       <c r="V71" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W71" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="W71" s="12">
+        <v>82</v>
+      </c>
       <c r="X71" s="10"/>
-      <c r="Y71" s="12"/>
+      <c r="Y71" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="Z71" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1534</v>
       </c>
       <c r="AA71" s="12">
         <f t="shared" si="21"/>
@@ -9963,24 +10192,28 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="19.5">
       <c r="A73" s="10">
         <v>8</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C73" s="10"/>
+      <c r="C73" s="10">
+        <v>173</v>
+      </c>
       <c r="D73" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E73" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="E73" s="12">
+        <v>0</v>
+      </c>
       <c r="F73" s="10"/>
       <c r="G73" s="12"/>
       <c r="H73" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="I73" s="12">
         <f t="shared" si="3"/>
@@ -9988,14 +10221,16 @@
       </c>
       <c r="J73" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K73" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="K73" s="12">
+        <v>0</v>
+      </c>
       <c r="L73" s="10"/>
       <c r="M73" s="12"/>
       <c r="N73" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="O73" s="12">
         <f t="shared" si="17"/>
@@ -10003,14 +10238,16 @@
       </c>
       <c r="P73" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q73" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="Q73" s="12">
+        <v>0</v>
+      </c>
       <c r="R73" s="10"/>
       <c r="S73" s="12"/>
       <c r="T73" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="U73" s="12">
         <f t="shared" si="19"/>
@@ -10018,38 +10255,44 @@
       </c>
       <c r="V73" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W73" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="W73" s="12">
+        <v>0</v>
+      </c>
       <c r="X73" s="10"/>
       <c r="Y73" s="12"/>
       <c r="Z73" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="AA73" s="12">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>8</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C74" s="10"/>
+      <c r="C74" s="10">
+        <v>173</v>
+      </c>
       <c r="D74" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E74" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="E74" s="12">
+        <v>0</v>
+      </c>
       <c r="F74" s="10"/>
       <c r="G74" s="12"/>
       <c r="H74" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="I74" s="12">
         <f t="shared" si="3"/>
@@ -10057,14 +10300,16 @@
       </c>
       <c r="J74" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K74" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="K74" s="12">
+        <v>0</v>
+      </c>
       <c r="L74" s="10"/>
       <c r="M74" s="12"/>
       <c r="N74" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="O74" s="12">
         <f t="shared" si="17"/>
@@ -10072,14 +10317,16 @@
       </c>
       <c r="P74" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q74" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="Q74" s="12">
+        <v>0</v>
+      </c>
       <c r="R74" s="10"/>
       <c r="S74" s="12"/>
       <c r="T74" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="U74" s="12">
         <f t="shared" si="19"/>
@@ -10087,38 +10334,44 @@
       </c>
       <c r="V74" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W74" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="W74" s="12">
+        <v>0</v>
+      </c>
       <c r="X74" s="10"/>
       <c r="Y74" s="12"/>
       <c r="Z74" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="AA74" s="12">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>8</v>
       </c>
       <c r="B75" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C75" s="10"/>
+      <c r="C75" s="10">
+        <v>173</v>
+      </c>
       <c r="D75" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E75" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="E75" s="12">
+        <v>0</v>
+      </c>
       <c r="F75" s="10"/>
       <c r="G75" s="12"/>
       <c r="H75" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="I75" s="12">
         <f t="shared" si="3"/>
@@ -10126,14 +10379,16 @@
       </c>
       <c r="J75" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K75" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="K75" s="12">
+        <v>0</v>
+      </c>
       <c r="L75" s="10"/>
       <c r="M75" s="12"/>
       <c r="N75" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="O75" s="12">
         <f t="shared" si="17"/>
@@ -10141,14 +10396,16 @@
       </c>
       <c r="P75" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q75" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="Q75" s="12">
+        <v>0</v>
+      </c>
       <c r="R75" s="10"/>
       <c r="S75" s="12"/>
       <c r="T75" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="U75" s="12">
         <f t="shared" si="19"/>
@@ -10156,38 +10413,44 @@
       </c>
       <c r="V75" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W75" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="W75" s="12">
+        <v>0</v>
+      </c>
       <c r="X75" s="10"/>
       <c r="Y75" s="12"/>
       <c r="Z75" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="AA75" s="12">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="10">
         <v>8</v>
       </c>
       <c r="B76" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C76" s="10"/>
+      <c r="C76" s="10">
+        <v>173</v>
+      </c>
       <c r="D76" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E76" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="E76" s="12">
+        <v>0</v>
+      </c>
       <c r="F76" s="10"/>
       <c r="G76" s="12"/>
       <c r="H76" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="I76" s="12">
         <f t="shared" si="3"/>
@@ -10195,14 +10458,16 @@
       </c>
       <c r="J76" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K76" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="K76" s="12">
+        <v>0</v>
+      </c>
       <c r="L76" s="10"/>
       <c r="M76" s="12"/>
       <c r="N76" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="O76" s="12">
         <f t="shared" si="17"/>
@@ -10210,14 +10475,16 @@
       </c>
       <c r="P76" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q76" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="Q76" s="12">
+        <v>0</v>
+      </c>
       <c r="R76" s="10"/>
       <c r="S76" s="12"/>
       <c r="T76" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="U76" s="12">
         <f t="shared" si="19"/>
@@ -10225,38 +10492,44 @@
       </c>
       <c r="V76" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W76" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="W76" s="12">
+        <v>0</v>
+      </c>
       <c r="X76" s="10"/>
       <c r="Y76" s="12"/>
       <c r="Z76" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="AA76" s="12">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>8</v>
       </c>
       <c r="B77" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C77" s="10"/>
+      <c r="C77" s="10">
+        <v>173</v>
+      </c>
       <c r="D77" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E77" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="E77" s="12">
+        <v>0</v>
+      </c>
       <c r="F77" s="10"/>
       <c r="G77" s="12"/>
       <c r="H77" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="I77" s="12">
         <f t="shared" si="3"/>
@@ -10264,14 +10537,16 @@
       </c>
       <c r="J77" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K77" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="K77" s="12">
+        <v>0</v>
+      </c>
       <c r="L77" s="10"/>
       <c r="M77" s="12"/>
       <c r="N77" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="O77" s="12">
         <f t="shared" si="17"/>
@@ -10279,14 +10554,16 @@
       </c>
       <c r="P77" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q77" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="Q77" s="12">
+        <v>0</v>
+      </c>
       <c r="R77" s="10"/>
       <c r="S77" s="12"/>
       <c r="T77" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="U77" s="12">
         <f t="shared" si="19"/>
@@ -10294,38 +10571,44 @@
       </c>
       <c r="V77" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W77" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="W77" s="12">
+        <v>0</v>
+      </c>
       <c r="X77" s="10"/>
       <c r="Y77" s="12"/>
       <c r="Z77" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="AA77" s="12">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" ht="19.5">
       <c r="A78" s="10">
         <v>8</v>
       </c>
       <c r="B78" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C78" s="10"/>
+      <c r="C78" s="10">
+        <v>173</v>
+      </c>
       <c r="D78" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E78" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="E78" s="12">
+        <v>0</v>
+      </c>
       <c r="F78" s="10"/>
       <c r="G78" s="12"/>
       <c r="H78" s="12">
         <f t="shared" ref="H78:H127" si="22">IF((D78-E78)&lt;0,0,(D78-E78))</f>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="I78" s="12">
         <f t="shared" ref="I78:I127" si="23">IF((E78-D78)&lt;0,0,(E78-D78))</f>
@@ -10333,14 +10616,16 @@
       </c>
       <c r="J78" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K78" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="K78" s="12">
+        <v>0</v>
+      </c>
       <c r="L78" s="10"/>
       <c r="M78" s="12"/>
       <c r="N78" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="O78" s="12">
         <f t="shared" si="17"/>
@@ -10348,14 +10633,16 @@
       </c>
       <c r="P78" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q78" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="Q78" s="12">
+        <v>0</v>
+      </c>
       <c r="R78" s="10"/>
       <c r="S78" s="12"/>
       <c r="T78" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="U78" s="12">
         <f t="shared" si="19"/>
@@ -10363,38 +10650,44 @@
       </c>
       <c r="V78" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W78" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="W78" s="12">
+        <v>0</v>
+      </c>
       <c r="X78" s="10"/>
       <c r="Y78" s="12"/>
       <c r="Z78" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="AA78" s="12">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
       <c r="B79" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C79" s="10"/>
+      <c r="C79" s="10">
+        <v>173</v>
+      </c>
       <c r="D79" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E79" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="E79" s="12">
+        <v>0</v>
+      </c>
       <c r="F79" s="10"/>
       <c r="G79" s="12"/>
       <c r="H79" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="I79" s="12">
         <f t="shared" si="23"/>
@@ -10402,14 +10695,16 @@
       </c>
       <c r="J79" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K79" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="K79" s="12">
+        <v>0</v>
+      </c>
       <c r="L79" s="10"/>
       <c r="M79" s="12"/>
       <c r="N79" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="O79" s="12">
         <f t="shared" si="17"/>
@@ -10417,14 +10712,16 @@
       </c>
       <c r="P79" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q79" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="Q79" s="12">
+        <v>0</v>
+      </c>
       <c r="R79" s="10"/>
       <c r="S79" s="12"/>
       <c r="T79" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="U79" s="12">
         <f t="shared" si="19"/>
@@ -10432,38 +10729,44 @@
       </c>
       <c r="V79" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W79" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="W79" s="12">
+        <v>0</v>
+      </c>
       <c r="X79" s="10"/>
       <c r="Y79" s="12"/>
       <c r="Z79" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="AA79" s="12">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
       <c r="B80" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C80" s="10"/>
+      <c r="C80" s="10">
+        <v>173</v>
+      </c>
       <c r="D80" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E80" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="E80" s="12">
+        <v>0</v>
+      </c>
       <c r="F80" s="10"/>
       <c r="G80" s="12"/>
       <c r="H80" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="I80" s="12">
         <f t="shared" si="23"/>
@@ -10471,14 +10774,16 @@
       </c>
       <c r="J80" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K80" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="K80" s="12">
+        <v>0</v>
+      </c>
       <c r="L80" s="10"/>
       <c r="M80" s="12"/>
       <c r="N80" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="O80" s="12">
         <f t="shared" si="17"/>
@@ -10486,14 +10791,16 @@
       </c>
       <c r="P80" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q80" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="Q80" s="12">
+        <v>0</v>
+      </c>
       <c r="R80" s="10"/>
       <c r="S80" s="12"/>
       <c r="T80" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="U80" s="12">
         <f t="shared" si="19"/>
@@ -10501,38 +10808,44 @@
       </c>
       <c r="V80" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W80" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="W80" s="12">
+        <v>0</v>
+      </c>
       <c r="X80" s="10"/>
       <c r="Y80" s="12"/>
       <c r="Z80" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="AA80" s="12">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
       <c r="B81" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C81" s="10"/>
+      <c r="C81" s="10">
+        <v>173</v>
+      </c>
       <c r="D81" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E81" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="E81" s="12">
+        <v>0</v>
+      </c>
       <c r="F81" s="10"/>
       <c r="G81" s="12"/>
       <c r="H81" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="I81" s="12">
         <f t="shared" si="23"/>
@@ -10540,14 +10853,16 @@
       </c>
       <c r="J81" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K81" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="K81" s="12">
+        <v>0</v>
+      </c>
       <c r="L81" s="10"/>
       <c r="M81" s="12"/>
       <c r="N81" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="O81" s="12">
         <f t="shared" si="17"/>
@@ -10555,14 +10870,16 @@
       </c>
       <c r="P81" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q81" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="Q81" s="12">
+        <v>0</v>
+      </c>
       <c r="R81" s="10"/>
       <c r="S81" s="12"/>
       <c r="T81" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="U81" s="12">
         <f t="shared" si="19"/>
@@ -10570,14 +10887,16 @@
       </c>
       <c r="V81" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W81" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="W81" s="12">
+        <v>0</v>
+      </c>
       <c r="X81" s="10"/>
       <c r="Y81" s="12"/>
       <c r="Z81" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="AA81" s="12">
         <f t="shared" si="21"/>
@@ -10598,24 +10917,28 @@
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="19.5">
       <c r="A83" s="10">
         <v>9</v>
       </c>
       <c r="B83" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C83" s="10"/>
+      <c r="C83" s="10">
+        <v>169</v>
+      </c>
       <c r="D83" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E83" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="E83" s="12">
+        <v>0</v>
+      </c>
       <c r="F83" s="10"/>
       <c r="G83" s="12"/>
       <c r="H83" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="I83" s="12">
         <f t="shared" si="23"/>
@@ -10623,14 +10946,16 @@
       </c>
       <c r="J83" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K83" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="K83" s="12">
+        <v>0</v>
+      </c>
       <c r="L83" s="10"/>
       <c r="M83" s="12"/>
       <c r="N83" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="O83" s="12">
         <f t="shared" si="17"/>
@@ -10638,14 +10963,16 @@
       </c>
       <c r="P83" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q83" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="Q83" s="12">
+        <v>0</v>
+      </c>
       <c r="R83" s="10"/>
       <c r="S83" s="12"/>
       <c r="T83" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="U83" s="12">
         <f t="shared" si="19"/>
@@ -10653,38 +10980,44 @@
       </c>
       <c r="V83" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W83" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="W83" s="12">
+        <v>0</v>
+      </c>
       <c r="X83" s="10"/>
       <c r="Y83" s="12"/>
       <c r="Z83" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="AA83" s="12">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>9</v>
       </c>
       <c r="B84" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C84" s="10"/>
+      <c r="C84" s="10">
+        <v>169</v>
+      </c>
       <c r="D84" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E84" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="E84" s="12">
+        <v>0</v>
+      </c>
       <c r="F84" s="10"/>
       <c r="G84" s="12"/>
       <c r="H84" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="I84" s="12">
         <f t="shared" si="23"/>
@@ -10692,14 +11025,16 @@
       </c>
       <c r="J84" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K84" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="K84" s="12">
+        <v>0</v>
+      </c>
       <c r="L84" s="10"/>
       <c r="M84" s="12"/>
       <c r="N84" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="O84" s="12">
         <f t="shared" si="17"/>
@@ -10707,14 +11042,16 @@
       </c>
       <c r="P84" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q84" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="Q84" s="12">
+        <v>0</v>
+      </c>
       <c r="R84" s="10"/>
       <c r="S84" s="12"/>
       <c r="T84" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="U84" s="12">
         <f t="shared" si="19"/>
@@ -10722,38 +11059,44 @@
       </c>
       <c r="V84" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W84" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="W84" s="12">
+        <v>0</v>
+      </c>
       <c r="X84" s="10"/>
       <c r="Y84" s="12"/>
       <c r="Z84" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="AA84" s="12">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="19.5">
       <c r="A85" s="10">
         <v>9</v>
       </c>
       <c r="B85" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C85" s="10"/>
+      <c r="C85" s="10">
+        <v>169</v>
+      </c>
       <c r="D85" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E85" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="E85" s="12">
+        <v>0</v>
+      </c>
       <c r="F85" s="10"/>
       <c r="G85" s="12"/>
       <c r="H85" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="I85" s="12">
         <f t="shared" si="23"/>
@@ -10761,14 +11104,16 @@
       </c>
       <c r="J85" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K85" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="K85" s="12">
+        <v>0</v>
+      </c>
       <c r="L85" s="10"/>
       <c r="M85" s="12"/>
       <c r="N85" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="O85" s="12">
         <f t="shared" si="17"/>
@@ -10776,14 +11121,16 @@
       </c>
       <c r="P85" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q85" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="Q85" s="12">
+        <v>0</v>
+      </c>
       <c r="R85" s="10"/>
       <c r="S85" s="12"/>
       <c r="T85" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="U85" s="12">
         <f t="shared" si="19"/>
@@ -10791,38 +11138,44 @@
       </c>
       <c r="V85" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W85" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="W85" s="12">
+        <v>0</v>
+      </c>
       <c r="X85" s="10"/>
       <c r="Y85" s="12"/>
       <c r="Z85" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="AA85" s="12">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>9</v>
       </c>
       <c r="B86" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C86" s="10"/>
+      <c r="C86" s="10">
+        <v>169</v>
+      </c>
       <c r="D86" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E86" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="E86" s="12">
+        <v>0</v>
+      </c>
       <c r="F86" s="10"/>
       <c r="G86" s="12"/>
       <c r="H86" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="I86" s="12">
         <f t="shared" si="23"/>
@@ -10830,14 +11183,16 @@
       </c>
       <c r="J86" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K86" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="K86" s="12">
+        <v>0</v>
+      </c>
       <c r="L86" s="10"/>
       <c r="M86" s="12"/>
       <c r="N86" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="O86" s="12">
         <f t="shared" si="17"/>
@@ -10845,14 +11200,16 @@
       </c>
       <c r="P86" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q86" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="Q86" s="12">
+        <v>0</v>
+      </c>
       <c r="R86" s="10"/>
       <c r="S86" s="12"/>
       <c r="T86" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="U86" s="12">
         <f t="shared" si="19"/>
@@ -10860,38 +11217,44 @@
       </c>
       <c r="V86" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W86" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="W86" s="12">
+        <v>0</v>
+      </c>
       <c r="X86" s="10"/>
       <c r="Y86" s="12"/>
       <c r="Z86" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="AA86" s="12">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>9</v>
       </c>
       <c r="B87" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C87" s="10"/>
+      <c r="C87" s="10">
+        <v>169</v>
+      </c>
       <c r="D87" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E87" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="E87" s="12">
+        <v>0</v>
+      </c>
       <c r="F87" s="10"/>
       <c r="G87" s="12"/>
       <c r="H87" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="I87" s="12">
         <f t="shared" si="23"/>
@@ -10899,14 +11262,16 @@
       </c>
       <c r="J87" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K87" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="K87" s="12">
+        <v>0</v>
+      </c>
       <c r="L87" s="10"/>
       <c r="M87" s="12"/>
       <c r="N87" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="O87" s="12">
         <f t="shared" si="17"/>
@@ -10914,14 +11279,16 @@
       </c>
       <c r="P87" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q87" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="Q87" s="12">
+        <v>0</v>
+      </c>
       <c r="R87" s="10"/>
       <c r="S87" s="12"/>
       <c r="T87" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="U87" s="12">
         <f t="shared" si="19"/>
@@ -10929,38 +11296,44 @@
       </c>
       <c r="V87" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W87" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="W87" s="12">
+        <v>0</v>
+      </c>
       <c r="X87" s="10"/>
       <c r="Y87" s="12"/>
       <c r="Z87" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="AA87" s="12">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="19.5">
       <c r="A88" s="10">
         <v>9</v>
       </c>
       <c r="B88" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C88" s="10"/>
+      <c r="C88" s="10">
+        <v>169</v>
+      </c>
       <c r="D88" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E88" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="E88" s="12">
+        <v>0</v>
+      </c>
       <c r="F88" s="10"/>
       <c r="G88" s="12"/>
       <c r="H88" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="I88" s="12">
         <f t="shared" si="23"/>
@@ -10968,14 +11341,16 @@
       </c>
       <c r="J88" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K88" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="K88" s="12">
+        <v>0</v>
+      </c>
       <c r="L88" s="10"/>
       <c r="M88" s="12"/>
       <c r="N88" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="O88" s="12">
         <f t="shared" si="17"/>
@@ -10983,14 +11358,16 @@
       </c>
       <c r="P88" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q88" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="Q88" s="12">
+        <v>0</v>
+      </c>
       <c r="R88" s="10"/>
       <c r="S88" s="12"/>
       <c r="T88" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="U88" s="12">
         <f t="shared" si="19"/>
@@ -10998,38 +11375,44 @@
       </c>
       <c r="V88" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W88" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="W88" s="12">
+        <v>0</v>
+      </c>
       <c r="X88" s="10"/>
       <c r="Y88" s="12"/>
       <c r="Z88" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="AA88" s="12">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>9</v>
       </c>
       <c r="B89" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C89" s="10"/>
+      <c r="C89" s="10">
+        <v>169</v>
+      </c>
       <c r="D89" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E89" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="E89" s="12">
+        <v>0</v>
+      </c>
       <c r="F89" s="10"/>
       <c r="G89" s="12"/>
       <c r="H89" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="I89" s="12">
         <f t="shared" si="23"/>
@@ -11037,14 +11420,16 @@
       </c>
       <c r="J89" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K89" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="K89" s="12">
+        <v>0</v>
+      </c>
       <c r="L89" s="10"/>
       <c r="M89" s="12"/>
       <c r="N89" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="O89" s="12">
         <f t="shared" si="17"/>
@@ -11052,14 +11437,16 @@
       </c>
       <c r="P89" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q89" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="Q89" s="12">
+        <v>0</v>
+      </c>
       <c r="R89" s="10"/>
       <c r="S89" s="12"/>
       <c r="T89" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="U89" s="12">
         <f t="shared" si="19"/>
@@ -11067,38 +11454,44 @@
       </c>
       <c r="V89" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W89" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="W89" s="12">
+        <v>0</v>
+      </c>
       <c r="X89" s="10"/>
       <c r="Y89" s="12"/>
       <c r="Z89" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="AA89" s="12">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" ht="19.5">
       <c r="A90" s="10">
         <v>9</v>
       </c>
       <c r="B90" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C90" s="10"/>
+      <c r="C90" s="10">
+        <v>169</v>
+      </c>
       <c r="D90" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E90" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="E90" s="12">
+        <v>0</v>
+      </c>
       <c r="F90" s="10"/>
       <c r="G90" s="12"/>
       <c r="H90" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="I90" s="12">
         <f t="shared" si="23"/>
@@ -11106,14 +11499,16 @@
       </c>
       <c r="J90" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K90" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="K90" s="12">
+        <v>0</v>
+      </c>
       <c r="L90" s="10"/>
       <c r="M90" s="12"/>
       <c r="N90" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="O90" s="12">
         <f t="shared" si="17"/>
@@ -11121,14 +11516,16 @@
       </c>
       <c r="P90" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q90" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="Q90" s="12">
+        <v>0</v>
+      </c>
       <c r="R90" s="10"/>
       <c r="S90" s="12"/>
       <c r="T90" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="U90" s="12">
         <f t="shared" si="19"/>
@@ -11136,38 +11533,44 @@
       </c>
       <c r="V90" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W90" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="W90" s="12">
+        <v>0</v>
+      </c>
       <c r="X90" s="10"/>
       <c r="Y90" s="12"/>
       <c r="Z90" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="AA90" s="12">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
       <c r="B91" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C91" s="10"/>
+      <c r="C91" s="10">
+        <v>169</v>
+      </c>
       <c r="D91" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E91" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="E91" s="12">
+        <v>0</v>
+      </c>
       <c r="F91" s="10"/>
       <c r="G91" s="12"/>
       <c r="H91" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="I91" s="12">
         <f t="shared" si="23"/>
@@ -11175,14 +11578,16 @@
       </c>
       <c r="J91" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K91" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="K91" s="12">
+        <v>0</v>
+      </c>
       <c r="L91" s="10"/>
       <c r="M91" s="12"/>
       <c r="N91" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="O91" s="12">
         <f t="shared" si="17"/>
@@ -11190,14 +11595,16 @@
       </c>
       <c r="P91" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q91" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="Q91" s="12">
+        <v>0</v>
+      </c>
       <c r="R91" s="10"/>
       <c r="S91" s="12"/>
       <c r="T91" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="U91" s="12">
         <f t="shared" si="19"/>
@@ -11205,14 +11612,16 @@
       </c>
       <c r="V91" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W91" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="W91" s="12">
+        <v>0</v>
+      </c>
       <c r="X91" s="10"/>
       <c r="Y91" s="12"/>
       <c r="Z91" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="AA91" s="12">
         <f t="shared" si="21"/>
@@ -11233,24 +11642,28 @@
       <c r="Z92" s="13"/>
       <c r="AA92" s="13"/>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="19.5">
       <c r="A93" s="10">
         <v>10</v>
       </c>
       <c r="B93" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C93" s="10"/>
+      <c r="C93" s="10">
+        <v>130</v>
+      </c>
       <c r="D93" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E93" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="E93" s="12">
+        <v>0</v>
+      </c>
       <c r="F93" s="10"/>
       <c r="G93" s="12"/>
       <c r="H93" s="12">
         <f>IF((D93-E93)&lt;0,0,(D93-E93))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="I93" s="12">
         <f>IF((E93-D93)&lt;0,0,(E93-D93))</f>
@@ -11258,14 +11671,16 @@
       </c>
       <c r="J93" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K93" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="K93" s="12">
+        <v>0</v>
+      </c>
       <c r="L93" s="10"/>
       <c r="M93" s="12"/>
       <c r="N93" s="12">
         <f>IF((J93-K93)&lt;0,0,(J93-K93))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="O93" s="12">
         <f>IF((K93-J93)&lt;0,0,(K93-J93))</f>
@@ -11273,14 +11688,16 @@
       </c>
       <c r="P93" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q93" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="Q93" s="12">
+        <v>0</v>
+      </c>
       <c r="R93" s="10"/>
       <c r="S93" s="12"/>
       <c r="T93" s="12">
         <f>IF((P93-Q93)&lt;0,0,(P93-Q93))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="U93" s="12">
         <f>IF((Q93-P93)&lt;0,0,(Q93-P93))</f>
@@ -11288,38 +11705,44 @@
       </c>
       <c r="V93" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W93" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="W93" s="12">
+        <v>0</v>
+      </c>
       <c r="X93" s="10"/>
       <c r="Y93" s="12"/>
       <c r="Z93" s="12">
         <f>IF((V93-W93)&lt;0,0,(V93-W93))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="AA93" s="12">
         <f>IF((W93-V93)&lt;0,0,(W93-V93))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="19.5">
       <c r="A94" s="10">
         <v>10</v>
       </c>
       <c r="B94" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C94" s="10"/>
+      <c r="C94" s="10">
+        <v>130</v>
+      </c>
       <c r="D94" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E94" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="E94" s="12">
+        <v>0</v>
+      </c>
       <c r="F94" s="10"/>
       <c r="G94" s="12"/>
       <c r="H94" s="12">
         <f>IF((D94-E94)&lt;0,0,(D94-E94))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="I94" s="12">
         <f>IF((E94-D94)&lt;0,0,(E94-D94))</f>
@@ -11327,14 +11750,16 @@
       </c>
       <c r="J94" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K94" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="K94" s="12">
+        <v>0</v>
+      </c>
       <c r="L94" s="10"/>
       <c r="M94" s="12"/>
       <c r="N94" s="12">
         <f>IF((J94-K94)&lt;0,0,(J94-K94))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="O94" s="12">
         <f>IF((K94-J94)&lt;0,0,(K94-J94))</f>
@@ -11342,14 +11767,16 @@
       </c>
       <c r="P94" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q94" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="Q94" s="12">
+        <v>0</v>
+      </c>
       <c r="R94" s="10"/>
       <c r="S94" s="12"/>
       <c r="T94" s="12">
         <f>IF((P94-Q94)&lt;0,0,(P94-Q94))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="U94" s="12">
         <f>IF((Q94-P94)&lt;0,0,(Q94-P94))</f>
@@ -11357,38 +11784,44 @@
       </c>
       <c r="V94" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W94" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="W94" s="12">
+        <v>0</v>
+      </c>
       <c r="X94" s="10"/>
       <c r="Y94" s="12"/>
       <c r="Z94" s="12">
         <f>IF((V94-W94)&lt;0,0,(V94-W94))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="AA94" s="12">
         <f>IF((W94-V94)&lt;0,0,(W94-V94))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="19.5">
       <c r="A95" s="10">
         <v>10</v>
       </c>
       <c r="B95" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C95" s="10"/>
+      <c r="C95" s="10">
+        <v>130</v>
+      </c>
       <c r="D95" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E95" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="E95" s="12">
+        <v>0</v>
+      </c>
       <c r="F95" s="10"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12">
         <f>IF((D95-E95)&lt;0,0,(D95-E95))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="I95" s="12">
         <f>IF((E95-D95)&lt;0,0,(E95-D95))</f>
@@ -11396,14 +11829,16 @@
       </c>
       <c r="J95" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K95" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="K95" s="12">
+        <v>0</v>
+      </c>
       <c r="L95" s="10"/>
       <c r="M95" s="12"/>
       <c r="N95" s="12">
         <f>IF((J95-K95)&lt;0,0,(J95-K95))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="O95" s="12">
         <f>IF((K95-J95)&lt;0,0,(K95-J95))</f>
@@ -11411,14 +11846,16 @@
       </c>
       <c r="P95" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q95" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="Q95" s="12">
+        <v>0</v>
+      </c>
       <c r="R95" s="10"/>
       <c r="S95" s="12"/>
       <c r="T95" s="12">
         <f>IF((P95-Q95)&lt;0,0,(P95-Q95))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="U95" s="12">
         <f>IF((Q95-P95)&lt;0,0,(Q95-P95))</f>
@@ -11426,38 +11863,44 @@
       </c>
       <c r="V95" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W95" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="W95" s="12">
+        <v>0</v>
+      </c>
       <c r="X95" s="10"/>
       <c r="Y95" s="12"/>
       <c r="Z95" s="12">
         <f>IF((V95-W95)&lt;0,0,(V95-W95))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="AA95" s="12">
         <f>IF((W95-V95)&lt;0,0,(W95-V95))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="19.5">
       <c r="A96" s="10">
         <v>10</v>
       </c>
       <c r="B96" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C96" s="10"/>
+      <c r="C96" s="10">
+        <v>130</v>
+      </c>
       <c r="D96" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E96" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="E96" s="12">
+        <v>0</v>
+      </c>
       <c r="F96" s="10"/>
       <c r="G96" s="12"/>
       <c r="H96" s="12">
         <f>IF((D96-E96)&lt;0,0,(D96-E96))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="I96" s="12">
         <f>IF((E96-D96)&lt;0,0,(E96-D96))</f>
@@ -11465,14 +11908,16 @@
       </c>
       <c r="J96" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K96" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="K96" s="12">
+        <v>0</v>
+      </c>
       <c r="L96" s="10"/>
       <c r="M96" s="12"/>
       <c r="N96" s="12">
         <f>IF((J96-K96)&lt;0,0,(J96-K96))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="O96" s="12">
         <f>IF((K96-J96)&lt;0,0,(K96-J96))</f>
@@ -11480,14 +11925,16 @@
       </c>
       <c r="P96" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q96" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="Q96" s="12">
+        <v>0</v>
+      </c>
       <c r="R96" s="10"/>
       <c r="S96" s="12"/>
       <c r="T96" s="12">
         <f>IF((P96-Q96)&lt;0,0,(P96-Q96))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="U96" s="12">
         <f>IF((Q96-P96)&lt;0,0,(Q96-P96))</f>
@@ -11495,38 +11942,44 @@
       </c>
       <c r="V96" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W96" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="W96" s="12">
+        <v>0</v>
+      </c>
       <c r="X96" s="10"/>
       <c r="Y96" s="12"/>
       <c r="Z96" s="12">
         <f>IF((V96-W96)&lt;0,0,(V96-W96))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="AA96" s="12">
         <f>IF((W96-V96)&lt;0,0,(W96-V96))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="19.5">
       <c r="A97" s="10">
         <v>10</v>
       </c>
       <c r="B97" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C97" s="10"/>
+      <c r="C97" s="10">
+        <v>130</v>
+      </c>
       <c r="D97" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E97" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="E97" s="12">
+        <v>0</v>
+      </c>
       <c r="F97" s="10"/>
       <c r="G97" s="12"/>
       <c r="H97" s="12">
         <f>IF((D97-E97)&lt;0,0,(D97-E97))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="I97" s="12">
         <f>IF((E97-D97)&lt;0,0,(E97-D97))</f>
@@ -11534,14 +11987,16 @@
       </c>
       <c r="J97" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K97" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="K97" s="12">
+        <v>0</v>
+      </c>
       <c r="L97" s="10"/>
       <c r="M97" s="12"/>
       <c r="N97" s="12">
         <f>IF((J97-K97)&lt;0,0,(J97-K97))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="O97" s="12">
         <f>IF((K97-J97)&lt;0,0,(K97-J97))</f>
@@ -11549,14 +12004,16 @@
       </c>
       <c r="P97" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q97" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="Q97" s="12">
+        <v>0</v>
+      </c>
       <c r="R97" s="10"/>
       <c r="S97" s="12"/>
       <c r="T97" s="12">
         <f>IF((P97-Q97)&lt;0,0,(P97-Q97))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="U97" s="12">
         <f>IF((Q97-P97)&lt;0,0,(Q97-P97))</f>
@@ -11564,38 +12021,44 @@
       </c>
       <c r="V97" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W97" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="W97" s="12">
+        <v>0</v>
+      </c>
       <c r="X97" s="10"/>
       <c r="Y97" s="12"/>
       <c r="Z97" s="12">
         <f>IF((V97-W97)&lt;0,0,(V97-W97))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="AA97" s="12">
         <f>IF((W97-V97)&lt;0,0,(W97-V97))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="19.5">
       <c r="A98" s="10">
         <v>10</v>
       </c>
       <c r="B98" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C98" s="10"/>
+      <c r="C98" s="10">
+        <v>130</v>
+      </c>
       <c r="D98" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E98" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="E98" s="12">
+        <v>0</v>
+      </c>
       <c r="F98" s="10"/>
       <c r="G98" s="12"/>
       <c r="H98" s="12">
         <f>IF((D98-E98)&lt;0,0,(D98-E98))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="I98" s="12">
         <f>IF((E98-D98)&lt;0,0,(E98-D98))</f>
@@ -11603,14 +12066,16 @@
       </c>
       <c r="J98" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K98" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="K98" s="12">
+        <v>0</v>
+      </c>
       <c r="L98" s="10"/>
       <c r="M98" s="12"/>
       <c r="N98" s="12">
         <f>IF((J98-K98)&lt;0,0,(J98-K98))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="O98" s="12">
         <f>IF((K98-J98)&lt;0,0,(K98-J98))</f>
@@ -11618,14 +12083,16 @@
       </c>
       <c r="P98" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q98" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="Q98" s="12">
+        <v>0</v>
+      </c>
       <c r="R98" s="10"/>
       <c r="S98" s="12"/>
       <c r="T98" s="12">
         <f>IF((P98-Q98)&lt;0,0,(P98-Q98))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="U98" s="12">
         <f>IF((Q98-P98)&lt;0,0,(Q98-P98))</f>
@@ -11633,38 +12100,44 @@
       </c>
       <c r="V98" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W98" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="W98" s="12">
+        <v>0</v>
+      </c>
       <c r="X98" s="10"/>
       <c r="Y98" s="12"/>
       <c r="Z98" s="12">
         <f>IF((V98-W98)&lt;0,0,(V98-W98))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="AA98" s="12">
         <f>IF((W98-V98)&lt;0,0,(W98-V98))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="19.5">
       <c r="A99" s="10">
         <v>10</v>
       </c>
       <c r="B99" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C99" s="10"/>
+      <c r="C99" s="10">
+        <v>130</v>
+      </c>
       <c r="D99" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E99" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="E99" s="12">
+        <v>0</v>
+      </c>
       <c r="F99" s="10"/>
       <c r="G99" s="12"/>
       <c r="H99" s="12">
         <f>IF((D99-E99)&lt;0,0,(D99-E99))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="I99" s="12">
         <f>IF((E99-D99)&lt;0,0,(E99-D99))</f>
@@ -11672,14 +12145,16 @@
       </c>
       <c r="J99" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K99" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="K99" s="12">
+        <v>0</v>
+      </c>
       <c r="L99" s="10"/>
       <c r="M99" s="12"/>
       <c r="N99" s="12">
         <f>IF((J99-K99)&lt;0,0,(J99-K99))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="O99" s="12">
         <f>IF((K99-J99)&lt;0,0,(K99-J99))</f>
@@ -11687,14 +12162,16 @@
       </c>
       <c r="P99" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q99" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="Q99" s="12">
+        <v>0</v>
+      </c>
       <c r="R99" s="10"/>
       <c r="S99" s="12"/>
       <c r="T99" s="12">
         <f>IF((P99-Q99)&lt;0,0,(P99-Q99))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="U99" s="12">
         <f>IF((Q99-P99)&lt;0,0,(Q99-P99))</f>
@@ -11702,38 +12179,44 @@
       </c>
       <c r="V99" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W99" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="W99" s="12">
+        <v>0</v>
+      </c>
       <c r="X99" s="10"/>
       <c r="Y99" s="12"/>
       <c r="Z99" s="12">
         <f>IF((V99-W99)&lt;0,0,(V99-W99))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="AA99" s="12">
         <f>IF((W99-V99)&lt;0,0,(W99-V99))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="19.5">
       <c r="A100" s="10">
         <v>10</v>
       </c>
       <c r="B100" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C100" s="10"/>
+      <c r="C100" s="10">
+        <v>130</v>
+      </c>
       <c r="D100" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E100" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="E100" s="12">
+        <v>0</v>
+      </c>
       <c r="F100" s="10"/>
       <c r="G100" s="12"/>
       <c r="H100" s="12">
         <f>IF((D100-E100)&lt;0,0,(D100-E100))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="I100" s="12">
         <f>IF((E100-D100)&lt;0,0,(E100-D100))</f>
@@ -11741,14 +12224,16 @@
       </c>
       <c r="J100" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K100" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="K100" s="12">
+        <v>0</v>
+      </c>
       <c r="L100" s="10"/>
       <c r="M100" s="12"/>
       <c r="N100" s="12">
         <f>IF((J100-K100)&lt;0,0,(J100-K100))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="O100" s="12">
         <f>IF((K100-J100)&lt;0,0,(K100-J100))</f>
@@ -11756,14 +12241,16 @@
       </c>
       <c r="P100" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q100" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="Q100" s="12">
+        <v>0</v>
+      </c>
       <c r="R100" s="10"/>
       <c r="S100" s="12"/>
       <c r="T100" s="12">
         <f>IF((P100-Q100)&lt;0,0,(P100-Q100))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="U100" s="12">
         <f>IF((Q100-P100)&lt;0,0,(Q100-P100))</f>
@@ -11771,38 +12258,44 @@
       </c>
       <c r="V100" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W100" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="W100" s="12">
+        <v>0</v>
+      </c>
       <c r="X100" s="10"/>
       <c r="Y100" s="12"/>
       <c r="Z100" s="12">
         <f>IF((V100-W100)&lt;0,0,(V100-W100))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="AA100" s="12">
         <f>IF((W100-V100)&lt;0,0,(W100-V100))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>10</v>
       </c>
       <c r="B101" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C101" s="10"/>
+      <c r="C101" s="10">
+        <v>130</v>
+      </c>
       <c r="D101" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E101" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="E101" s="12">
+        <v>0</v>
+      </c>
       <c r="F101" s="10"/>
       <c r="G101" s="12"/>
       <c r="H101" s="12">
         <f>IF((D101-E101)&lt;0,0,(D101-E101))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="I101" s="12">
         <f>IF((E101-D101)&lt;0,0,(E101-D101))</f>
@@ -11810,14 +12303,16 @@
       </c>
       <c r="J101" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K101" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="K101" s="12">
+        <v>0</v>
+      </c>
       <c r="L101" s="10"/>
       <c r="M101" s="12"/>
       <c r="N101" s="12">
         <f>IF((J101-K101)&lt;0,0,(J101-K101))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="O101" s="12">
         <f>IF((K101-J101)&lt;0,0,(K101-J101))</f>
@@ -11825,14 +12320,16 @@
       </c>
       <c r="P101" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q101" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="Q101" s="12">
+        <v>0</v>
+      </c>
       <c r="R101" s="10"/>
       <c r="S101" s="12"/>
       <c r="T101" s="12">
         <f>IF((P101-Q101)&lt;0,0,(P101-Q101))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="U101" s="12">
         <f>IF((Q101-P101)&lt;0,0,(Q101-P101))</f>
@@ -11840,14 +12337,16 @@
       </c>
       <c r="V101" s="12">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W101" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="W101" s="12">
+        <v>0</v>
+      </c>
       <c r="X101" s="10"/>
       <c r="Y101" s="12"/>
       <c r="Z101" s="12">
         <f>IF((V101-W101)&lt;0,0,(V101-W101))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="AA101" s="12">
         <f>IF((W101-V101)&lt;0,0,(W101-V101))</f>
@@ -13420,191 +13919,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
+    <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C103:C110 C112:C127 C5:C12 C63:C71 C73:C81 C83:C91 C93:C101" name="Textbooks"/>
     <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13" name="LAS"/>
-    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
+    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110 Y14:Y110" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -13613,15 +13932,21 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 G103:G110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 Y14:Y110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61" xr:uid="{6C3E346F-6A45-48B1-ACC9-32B5BE0EEF9E}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F63:F71 F73:F81 F83:F91 F93:F101 F103:F110 F112:F127 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110 L112:L127 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101 X103:X110" xr:uid="{DBC188D9-FEC9-4916-BAEF-CDF568835B61}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13636,7 +13961,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -13666,38 +13991,38 @@
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -13710,76 +14035,76 @@
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K2" s="22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="M2" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="M2" s="40" t="s">
         <v>73</v>
       </c>
+      <c r="N2" s="40" t="s">
+        <v>74</v>
+      </c>
       <c r="O2" s="22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P2" s="24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q2" s="24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="R2" s="25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S2" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T2" s="17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U2" s="24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="V2" s="26" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W2" s="26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X2" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="Y2" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="Z2" s="45" t="s">
+      <c r="Y2" s="41" t="s">
         <v>85</v>
       </c>
+      <c r="Z2" s="41" t="s">
+        <v>86</v>
+      </c>
       <c r="AA2" s="26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="19.149999999999999">
@@ -15929,7 +16254,7 @@
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="5">
@@ -15998,7 +16323,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="5">
@@ -16136,7 +16461,7 @@
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5">
@@ -16205,7 +16530,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="5">
@@ -16689,7 +17014,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="5">
@@ -16758,7 +17083,7 @@
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="5">
@@ -16896,7 +17221,7 @@
         <v>5</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="5">
@@ -16965,7 +17290,7 @@
         <v>5</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="5">
@@ -17449,7 +17774,7 @@
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="5">
@@ -17518,7 +17843,7 @@
         <v>6</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="5">
@@ -17656,7 +17981,7 @@
         <v>6</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="5">
@@ -17725,7 +18050,7 @@
         <v>6</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="5">
@@ -17790,24 +18115,28 @@
       </c>
     </row>
     <row r="66" spans="1:27" s="7" customFormat="1"/>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="19.5">
       <c r="A67" s="10">
         <v>7</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C67" s="10"/>
+      <c r="C67" s="10">
+        <v>202</v>
+      </c>
       <c r="D67" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E67" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="E67" s="12">
+        <v>0</v>
+      </c>
       <c r="F67" s="10"/>
       <c r="G67" s="12"/>
       <c r="H67" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="I67" s="12">
         <f t="shared" si="1"/>
@@ -17815,14 +18144,16 @@
       </c>
       <c r="J67" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K67" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="K67" s="12">
+        <v>0</v>
+      </c>
       <c r="L67" s="10"/>
       <c r="M67" s="12"/>
       <c r="N67" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="O67" s="12">
         <f t="shared" si="3"/>
@@ -17830,14 +18161,16 @@
       </c>
       <c r="P67" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q67" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="Q67" s="12">
+        <v>0</v>
+      </c>
       <c r="R67" s="10"/>
       <c r="S67" s="12"/>
       <c r="T67" s="12">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="U67" s="12">
         <f t="shared" si="5"/>
@@ -17845,38 +18178,44 @@
       </c>
       <c r="V67" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W67" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="W67" s="12">
+        <v>0</v>
+      </c>
       <c r="X67" s="10"/>
       <c r="Y67" s="12"/>
       <c r="Z67" s="12">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="AA67" s="12">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C68" s="10"/>
+      <c r="C68" s="10">
+        <v>202</v>
+      </c>
       <c r="D68" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E68" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="E68" s="12">
+        <v>0</v>
+      </c>
       <c r="F68" s="10"/>
       <c r="G68" s="12"/>
       <c r="H68" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="I68" s="12">
         <f t="shared" si="1"/>
@@ -17884,14 +18223,16 @@
       </c>
       <c r="J68" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K68" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="K68" s="12">
+        <v>0</v>
+      </c>
       <c r="L68" s="10"/>
       <c r="M68" s="12"/>
       <c r="N68" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="O68" s="12">
         <f t="shared" si="3"/>
@@ -17899,14 +18240,16 @@
       </c>
       <c r="P68" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q68" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="Q68" s="12">
+        <v>0</v>
+      </c>
       <c r="R68" s="10"/>
       <c r="S68" s="12"/>
       <c r="T68" s="12">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="U68" s="12">
         <f t="shared" si="5"/>
@@ -17914,38 +18257,44 @@
       </c>
       <c r="V68" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W68" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="W68" s="12">
+        <v>0</v>
+      </c>
       <c r="X68" s="10"/>
       <c r="Y68" s="12"/>
       <c r="Z68" s="12">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="AA68" s="12">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C69" s="10"/>
+      <c r="C69" s="10">
+        <v>202</v>
+      </c>
       <c r="D69" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E69" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="E69" s="12">
+        <v>0</v>
+      </c>
       <c r="F69" s="10"/>
       <c r="G69" s="12"/>
       <c r="H69" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="I69" s="12">
         <f t="shared" si="1"/>
@@ -17953,14 +18302,16 @@
       </c>
       <c r="J69" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K69" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="K69" s="12">
+        <v>0</v>
+      </c>
       <c r="L69" s="10"/>
       <c r="M69" s="12"/>
       <c r="N69" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="O69" s="12">
         <f t="shared" si="3"/>
@@ -17968,14 +18319,16 @@
       </c>
       <c r="P69" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q69" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="Q69" s="12">
+        <v>0</v>
+      </c>
       <c r="R69" s="10"/>
       <c r="S69" s="12"/>
       <c r="T69" s="12">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="U69" s="12">
         <f t="shared" si="5"/>
@@ -17983,38 +18336,44 @@
       </c>
       <c r="V69" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W69" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="W69" s="12">
+        <v>0</v>
+      </c>
       <c r="X69" s="10"/>
       <c r="Y69" s="12"/>
       <c r="Z69" s="12">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="AA69" s="12">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C70" s="10"/>
+      <c r="C70" s="10">
+        <v>202</v>
+      </c>
       <c r="D70" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E70" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="E70" s="12">
+        <v>0</v>
+      </c>
       <c r="F70" s="10"/>
       <c r="G70" s="12"/>
       <c r="H70" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="I70" s="12">
         <f t="shared" si="1"/>
@@ -18022,14 +18381,16 @@
       </c>
       <c r="J70" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K70" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="K70" s="12">
+        <v>0</v>
+      </c>
       <c r="L70" s="10"/>
       <c r="M70" s="12"/>
       <c r="N70" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="O70" s="12">
         <f t="shared" si="3"/>
@@ -18037,14 +18398,16 @@
       </c>
       <c r="P70" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q70" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="Q70" s="12">
+        <v>0</v>
+      </c>
       <c r="R70" s="10"/>
       <c r="S70" s="12"/>
       <c r="T70" s="12">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="U70" s="12">
         <f t="shared" si="5"/>
@@ -18052,38 +18415,44 @@
       </c>
       <c r="V70" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W70" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="W70" s="12">
+        <v>0</v>
+      </c>
       <c r="X70" s="10"/>
       <c r="Y70" s="12"/>
       <c r="Z70" s="12">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="AA70" s="12">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="38.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C71" s="10"/>
+      <c r="C71" s="10">
+        <v>202</v>
+      </c>
       <c r="D71" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E71" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="E71" s="12">
+        <v>0</v>
+      </c>
       <c r="F71" s="10"/>
       <c r="G71" s="12"/>
       <c r="H71" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="I71" s="12">
         <f t="shared" si="1"/>
@@ -18091,14 +18460,16 @@
       </c>
       <c r="J71" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K71" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="K71" s="12">
+        <v>0</v>
+      </c>
       <c r="L71" s="10"/>
       <c r="M71" s="12"/>
       <c r="N71" s="12">
         <f t="shared" ref="N71:N77" si="14">IF((J71-K71)&lt;0,0,(J71-K71))</f>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="O71" s="12">
         <f t="shared" ref="O71:O77" si="15">IF((K71-J71)&lt;0,0,(K71-J71))</f>
@@ -18106,14 +18477,16 @@
       </c>
       <c r="P71" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q71" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="Q71" s="12">
+        <v>0</v>
+      </c>
       <c r="R71" s="10"/>
       <c r="S71" s="12"/>
       <c r="T71" s="12">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="U71" s="12">
         <f t="shared" si="5"/>
@@ -18121,38 +18494,44 @@
       </c>
       <c r="V71" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W71" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="W71" s="12">
+        <v>0</v>
+      </c>
       <c r="X71" s="10"/>
       <c r="Y71" s="12"/>
       <c r="Z71" s="12">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="AA71" s="12">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="19.149999999999999">
+    <row r="72" spans="1:27" ht="19.5">
       <c r="A72" s="10">
         <v>7</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C72" s="10"/>
+      <c r="C72" s="10">
+        <v>202</v>
+      </c>
       <c r="D72" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E72" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="E72" s="12">
+        <v>0</v>
+      </c>
       <c r="F72" s="10"/>
       <c r="G72" s="12"/>
       <c r="H72" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="I72" s="12">
         <f t="shared" si="1"/>
@@ -18160,14 +18539,16 @@
       </c>
       <c r="J72" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K72" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="K72" s="12">
+        <v>0</v>
+      </c>
       <c r="L72" s="10"/>
       <c r="M72" s="12"/>
       <c r="N72" s="12">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="O72" s="12">
         <f t="shared" si="15"/>
@@ -18175,14 +18556,16 @@
       </c>
       <c r="P72" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q72" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="Q72" s="12">
+        <v>0</v>
+      </c>
       <c r="R72" s="10"/>
       <c r="S72" s="12"/>
       <c r="T72" s="12">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="U72" s="12">
         <f t="shared" si="5"/>
@@ -18190,38 +18573,44 @@
       </c>
       <c r="V72" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W72" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="W72" s="12">
+        <v>0</v>
+      </c>
       <c r="X72" s="10"/>
       <c r="Y72" s="12"/>
       <c r="Z72" s="12">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="AA72" s="12">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="19.5">
       <c r="A73" s="38">
         <v>7</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C73" s="12"/>
+        <v>88</v>
+      </c>
+      <c r="C73" s="10">
+        <v>202</v>
+      </c>
       <c r="D73" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E73" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="E73" s="12">
+        <v>0</v>
+      </c>
       <c r="F73" s="10"/>
       <c r="G73" s="12"/>
       <c r="H73" s="12">
         <f>IF((D73-E73)&lt;0,0,(D73-E73))</f>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="I73" s="12">
         <f>IF((E73-D73)&lt;0,0,(E73-D73))</f>
@@ -18229,14 +18618,16 @@
       </c>
       <c r="J73" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K73" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="K73" s="12">
+        <v>0</v>
+      </c>
       <c r="L73" s="10"/>
       <c r="M73" s="12"/>
       <c r="N73" s="12">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="O73" s="12">
         <f t="shared" si="15"/>
@@ -18244,14 +18635,16 @@
       </c>
       <c r="P73" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q73" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="Q73" s="12">
+        <v>0</v>
+      </c>
       <c r="R73" s="10"/>
       <c r="S73" s="12"/>
       <c r="T73" s="12">
         <f>IF((P73-Q73)&lt;0,0,(P73-Q73))</f>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="U73" s="12">
         <f>IF((Q73-P73)&lt;0,0,(Q73-P73))</f>
@@ -18259,38 +18652,44 @@
       </c>
       <c r="V73" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W73" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="W73" s="12">
+        <v>0</v>
+      </c>
       <c r="X73" s="10"/>
       <c r="Y73" s="12"/>
       <c r="Z73" s="12">
         <f>IF((V73-W73)&lt;0,0,(V73-W73))</f>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="AA73" s="12">
         <f>IF((W73-V73)&lt;0,0,(W73-V73))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>7</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C74" s="10"/>
+        <v>89</v>
+      </c>
+      <c r="C74" s="10">
+        <v>202</v>
+      </c>
       <c r="D74" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E74" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="E74" s="12">
+        <v>0</v>
+      </c>
       <c r="F74" s="10"/>
       <c r="G74" s="12"/>
       <c r="H74" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="I74" s="12">
         <f t="shared" si="1"/>
@@ -18298,14 +18697,16 @@
       </c>
       <c r="J74" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K74" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="K74" s="12">
+        <v>0</v>
+      </c>
       <c r="L74" s="10"/>
       <c r="M74" s="12"/>
       <c r="N74" s="12">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="O74" s="12">
         <f t="shared" si="15"/>
@@ -18313,14 +18714,16 @@
       </c>
       <c r="P74" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q74" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="Q74" s="12">
+        <v>0</v>
+      </c>
       <c r="R74" s="10"/>
       <c r="S74" s="12"/>
       <c r="T74" s="12">
         <f t="shared" ref="T74:T122" si="16">IF((P74-Q74)&lt;0,0,(P74-Q74))</f>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="U74" s="12">
         <f t="shared" ref="U74:U122" si="17">IF((Q74-P74)&lt;0,0,(Q74-P74))</f>
@@ -18328,38 +18731,44 @@
       </c>
       <c r="V74" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W74" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="W74" s="12">
+        <v>0</v>
+      </c>
       <c r="X74" s="10"/>
       <c r="Y74" s="12"/>
       <c r="Z74" s="12">
         <f t="shared" ref="Z74:Z122" si="18">IF((V74-W74)&lt;0,0,(V74-W74))</f>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="AA74" s="12">
         <f t="shared" ref="AA74:AA122" si="19">IF((W74-V74)&lt;0,0,(W74-V74))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>7</v>
       </c>
       <c r="B75" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C75" s="10"/>
+      <c r="C75" s="10">
+        <v>202</v>
+      </c>
       <c r="D75" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E75" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="E75" s="12">
+        <v>0</v>
+      </c>
       <c r="F75" s="10"/>
       <c r="G75" s="12"/>
       <c r="H75" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="I75" s="12">
         <f t="shared" si="1"/>
@@ -18367,14 +18776,16 @@
       </c>
       <c r="J75" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K75" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="K75" s="12">
+        <v>0</v>
+      </c>
       <c r="L75" s="10"/>
       <c r="M75" s="12"/>
       <c r="N75" s="12">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="O75" s="12">
         <f t="shared" si="15"/>
@@ -18382,14 +18793,16 @@
       </c>
       <c r="P75" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q75" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="Q75" s="12">
+        <v>0</v>
+      </c>
       <c r="R75" s="10"/>
       <c r="S75" s="12"/>
       <c r="T75" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="U75" s="12">
         <f t="shared" si="17"/>
@@ -18397,38 +18810,44 @@
       </c>
       <c r="V75" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W75" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="W75" s="12">
+        <v>0</v>
+      </c>
       <c r="X75" s="10"/>
       <c r="Y75" s="12"/>
       <c r="Z75" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="AA75" s="12">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="38">
         <v>7</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C76" s="12"/>
+        <v>90</v>
+      </c>
+      <c r="C76" s="10">
+        <v>202</v>
+      </c>
       <c r="D76" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E76" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="E76" s="12">
+        <v>0</v>
+      </c>
       <c r="F76" s="10"/>
       <c r="G76" s="12"/>
       <c r="H76" s="12">
         <f>IF((D76-E76)&lt;0,0,(D76-E76))</f>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="I76" s="12">
         <f>IF((E76-D76)&lt;0,0,(E76-D76))</f>
@@ -18436,14 +18855,16 @@
       </c>
       <c r="J76" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K76" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="K76" s="12">
+        <v>0</v>
+      </c>
       <c r="L76" s="10"/>
       <c r="M76" s="12"/>
       <c r="N76" s="12">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="O76" s="12">
         <f t="shared" si="15"/>
@@ -18451,14 +18872,16 @@
       </c>
       <c r="P76" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q76" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="Q76" s="12">
+        <v>0</v>
+      </c>
       <c r="R76" s="10"/>
       <c r="S76" s="12"/>
       <c r="T76" s="12">
         <f>IF((P76-Q76)&lt;0,0,(P76-Q76))</f>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="U76" s="12">
         <f>IF((Q76-P76)&lt;0,0,(Q76-P76))</f>
@@ -18466,38 +18889,44 @@
       </c>
       <c r="V76" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W76" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="W76" s="12">
+        <v>0</v>
+      </c>
       <c r="X76" s="10"/>
       <c r="Y76" s="12"/>
       <c r="Z76" s="12">
         <f>IF((V76-W76)&lt;0,0,(V76-W76))</f>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="AA76" s="12">
         <f>IF((W76-V76)&lt;0,0,(W76-V76))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>7</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C77" s="10"/>
+        <v>91</v>
+      </c>
+      <c r="C77" s="10">
+        <v>202</v>
+      </c>
       <c r="D77" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E77" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="E77" s="12">
+        <v>0</v>
+      </c>
       <c r="F77" s="10"/>
       <c r="G77" s="12"/>
       <c r="H77" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="I77" s="12">
         <f t="shared" si="1"/>
@@ -18505,14 +18934,16 @@
       </c>
       <c r="J77" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K77" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="K77" s="12">
+        <v>0</v>
+      </c>
       <c r="L77" s="10"/>
       <c r="M77" s="12"/>
       <c r="N77" s="12">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="O77" s="12">
         <f t="shared" si="15"/>
@@ -18520,14 +18951,16 @@
       </c>
       <c r="P77" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q77" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="Q77" s="12">
+        <v>0</v>
+      </c>
       <c r="R77" s="10"/>
       <c r="S77" s="12"/>
       <c r="T77" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="U77" s="12">
         <f t="shared" si="17"/>
@@ -18535,14 +18968,16 @@
       </c>
       <c r="V77" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W77" s="12"/>
+        <v>1616</v>
+      </c>
+      <c r="W77" s="12">
+        <v>0</v>
+      </c>
       <c r="X77" s="10"/>
       <c r="Y77" s="12"/>
       <c r="Z77" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1616</v>
       </c>
       <c r="AA77" s="12">
         <f t="shared" si="19"/>
@@ -18550,24 +18985,28 @@
       </c>
     </row>
     <row r="78" spans="1:27" s="7" customFormat="1"/>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
       <c r="B79" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C79" s="10"/>
+      <c r="C79" s="10">
+        <v>173</v>
+      </c>
       <c r="D79" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E79" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="E79" s="12">
+        <v>0</v>
+      </c>
       <c r="F79" s="10"/>
       <c r="G79" s="12"/>
       <c r="H79" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="I79" s="12">
         <f t="shared" si="1"/>
@@ -18575,14 +19014,16 @@
       </c>
       <c r="J79" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K79" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="K79" s="12">
+        <v>0</v>
+      </c>
       <c r="L79" s="10"/>
       <c r="M79" s="12"/>
       <c r="N79" s="12">
         <f t="shared" ref="N74:N122" si="20">IF((J79-K79)&lt;0,0,(J79-K79))</f>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="O79" s="12">
         <f t="shared" ref="O74:O122" si="21">IF((K79-J79)&lt;0,0,(K79-J79))</f>
@@ -18590,14 +19031,16 @@
       </c>
       <c r="P79" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q79" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="Q79" s="12">
+        <v>0</v>
+      </c>
       <c r="R79" s="10"/>
       <c r="S79" s="12"/>
       <c r="T79" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="U79" s="12">
         <f t="shared" si="17"/>
@@ -18605,38 +19048,44 @@
       </c>
       <c r="V79" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W79" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="W79" s="12">
+        <v>0</v>
+      </c>
       <c r="X79" s="10"/>
       <c r="Y79" s="12"/>
       <c r="Z79" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="AA79" s="12">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
       <c r="B80" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C80" s="10"/>
+      <c r="C80" s="10">
+        <v>173</v>
+      </c>
       <c r="D80" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E80" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="E80" s="12">
+        <v>0</v>
+      </c>
       <c r="F80" s="10"/>
       <c r="G80" s="12"/>
       <c r="H80" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="I80" s="12">
         <f t="shared" si="1"/>
@@ -18644,14 +19093,16 @@
       </c>
       <c r="J80" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K80" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="K80" s="12">
+        <v>0</v>
+      </c>
       <c r="L80" s="10"/>
       <c r="M80" s="12"/>
       <c r="N80" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="O80" s="12">
         <f t="shared" si="21"/>
@@ -18659,14 +19110,16 @@
       </c>
       <c r="P80" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q80" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="Q80" s="12">
+        <v>0</v>
+      </c>
       <c r="R80" s="10"/>
       <c r="S80" s="12"/>
       <c r="T80" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="U80" s="12">
         <f t="shared" si="17"/>
@@ -18674,38 +19127,44 @@
       </c>
       <c r="V80" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W80" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="W80" s="12">
+        <v>0</v>
+      </c>
       <c r="X80" s="10"/>
       <c r="Y80" s="12"/>
       <c r="Z80" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="AA80" s="12">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
       <c r="B81" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C81" s="10"/>
+      <c r="C81" s="10">
+        <v>173</v>
+      </c>
       <c r="D81" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E81" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="E81" s="12">
+        <v>0</v>
+      </c>
       <c r="F81" s="10"/>
       <c r="G81" s="12"/>
       <c r="H81" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="I81" s="12">
         <f t="shared" si="1"/>
@@ -18713,14 +19172,16 @@
       </c>
       <c r="J81" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K81" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="K81" s="12">
+        <v>0</v>
+      </c>
       <c r="L81" s="10"/>
       <c r="M81" s="12"/>
       <c r="N81" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="O81" s="12">
         <f t="shared" si="21"/>
@@ -18728,14 +19189,16 @@
       </c>
       <c r="P81" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q81" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="Q81" s="12">
+        <v>0</v>
+      </c>
       <c r="R81" s="10"/>
       <c r="S81" s="12"/>
       <c r="T81" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="U81" s="12">
         <f t="shared" si="17"/>
@@ -18743,38 +19206,44 @@
       </c>
       <c r="V81" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W81" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="W81" s="12">
+        <v>0</v>
+      </c>
       <c r="X81" s="10"/>
       <c r="Y81" s="12"/>
       <c r="Z81" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="AA81" s="12">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="19.149999999999999">
+    <row r="82" spans="1:27" ht="19.5">
       <c r="A82" s="10">
         <v>8</v>
       </c>
       <c r="B82" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C82" s="10"/>
+      <c r="C82" s="10">
+        <v>173</v>
+      </c>
       <c r="D82" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E82" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="E82" s="12">
+        <v>0</v>
+      </c>
       <c r="F82" s="10"/>
       <c r="G82" s="12"/>
       <c r="H82" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="I82" s="12">
         <f t="shared" si="1"/>
@@ -18782,14 +19251,16 @@
       </c>
       <c r="J82" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K82" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="K82" s="12">
+        <v>0</v>
+      </c>
       <c r="L82" s="10"/>
       <c r="M82" s="12"/>
       <c r="N82" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="O82" s="12">
         <f t="shared" si="21"/>
@@ -18797,14 +19268,16 @@
       </c>
       <c r="P82" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q82" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="Q82" s="12">
+        <v>0</v>
+      </c>
       <c r="R82" s="10"/>
       <c r="S82" s="12"/>
       <c r="T82" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="U82" s="12">
         <f t="shared" si="17"/>
@@ -18812,38 +19285,44 @@
       </c>
       <c r="V82" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W82" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="W82" s="12">
+        <v>0</v>
+      </c>
       <c r="X82" s="10"/>
       <c r="Y82" s="12"/>
       <c r="Z82" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="AA82" s="12">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="19.5">
       <c r="A83" s="10">
         <v>8</v>
       </c>
       <c r="B83" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C83" s="10"/>
+      <c r="C83" s="10">
+        <v>173</v>
+      </c>
       <c r="D83" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E83" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="E83" s="12">
+        <v>0</v>
+      </c>
       <c r="F83" s="10"/>
       <c r="G83" s="12"/>
       <c r="H83" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="I83" s="12">
         <f t="shared" si="1"/>
@@ -18851,14 +19330,16 @@
       </c>
       <c r="J83" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K83" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="K83" s="12">
+        <v>0</v>
+      </c>
       <c r="L83" s="10"/>
       <c r="M83" s="12"/>
       <c r="N83" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="O83" s="12">
         <f t="shared" si="21"/>
@@ -18866,14 +19347,16 @@
       </c>
       <c r="P83" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q83" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="Q83" s="12">
+        <v>0</v>
+      </c>
       <c r="R83" s="10"/>
       <c r="S83" s="12"/>
       <c r="T83" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="U83" s="12">
         <f t="shared" si="17"/>
@@ -18881,38 +19364,44 @@
       </c>
       <c r="V83" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W83" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="W83" s="12">
+        <v>0</v>
+      </c>
       <c r="X83" s="10"/>
       <c r="Y83" s="12"/>
       <c r="Z83" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="AA83" s="12">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>8</v>
       </c>
       <c r="B84" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C84" s="10"/>
+      <c r="C84" s="10">
+        <v>173</v>
+      </c>
       <c r="D84" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E84" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="E84" s="12">
+        <v>0</v>
+      </c>
       <c r="F84" s="10"/>
       <c r="G84" s="12"/>
       <c r="H84" s="12">
         <f t="shared" ref="H84:H122" si="22">IF((D84-E84)&lt;0,0,(D84-E84))</f>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="I84" s="12">
         <f t="shared" ref="I84:I122" si="23">IF((E84-D84)&lt;0,0,(E84-D84))</f>
@@ -18920,14 +19409,16 @@
       </c>
       <c r="J84" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K84" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="K84" s="12">
+        <v>0</v>
+      </c>
       <c r="L84" s="10"/>
       <c r="M84" s="12"/>
       <c r="N84" s="12">
         <f t="shared" ref="N84:N89" si="24">IF((J84-K84)&lt;0,0,(J84-K84))</f>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="O84" s="12">
         <f t="shared" ref="O84:O89" si="25">IF((K84-J84)&lt;0,0,(K84-J84))</f>
@@ -18935,14 +19426,16 @@
       </c>
       <c r="P84" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q84" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="Q84" s="12">
+        <v>0</v>
+      </c>
       <c r="R84" s="10"/>
       <c r="S84" s="12"/>
       <c r="T84" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="U84" s="12">
         <f t="shared" si="17"/>
@@ -18950,38 +19443,44 @@
       </c>
       <c r="V84" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W84" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="W84" s="12">
+        <v>0</v>
+      </c>
       <c r="X84" s="10"/>
       <c r="Y84" s="12"/>
       <c r="Z84" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="AA84" s="12">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="19.5">
       <c r="A85" s="38">
         <v>8</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C85" s="12"/>
+        <v>88</v>
+      </c>
+      <c r="C85" s="10">
+        <v>173</v>
+      </c>
       <c r="D85" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E85" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="E85" s="12">
+        <v>0</v>
+      </c>
       <c r="F85" s="10"/>
       <c r="G85" s="12"/>
       <c r="H85" s="12">
         <f>IF((D85-E85)&lt;0,0,(D85-E85))</f>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="I85" s="12">
         <f>IF((E85-D85)&lt;0,0,(E85-D85))</f>
@@ -18989,14 +19488,16 @@
       </c>
       <c r="J85" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K85" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="K85" s="12">
+        <v>0</v>
+      </c>
       <c r="L85" s="10"/>
       <c r="M85" s="12"/>
       <c r="N85" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="O85" s="12">
         <f t="shared" si="25"/>
@@ -19004,14 +19505,16 @@
       </c>
       <c r="P85" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q85" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="Q85" s="12">
+        <v>0</v>
+      </c>
       <c r="R85" s="10"/>
       <c r="S85" s="12"/>
       <c r="T85" s="12">
         <f>IF((P85-Q85)&lt;0,0,(P85-Q85))</f>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="U85" s="12">
         <f>IF((Q85-P85)&lt;0,0,(Q85-P85))</f>
@@ -19019,38 +19522,44 @@
       </c>
       <c r="V85" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W85" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="W85" s="12">
+        <v>0</v>
+      </c>
       <c r="X85" s="10"/>
       <c r="Y85" s="12"/>
       <c r="Z85" s="12">
         <f>IF((V85-W85)&lt;0,0,(V85-W85))</f>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="AA85" s="12">
         <f>IF((W85-V85)&lt;0,0,(W85-V85))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>8</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C86" s="10"/>
+        <v>89</v>
+      </c>
+      <c r="C86" s="10">
+        <v>173</v>
+      </c>
       <c r="D86" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E86" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="E86" s="12">
+        <v>0</v>
+      </c>
       <c r="F86" s="10"/>
       <c r="G86" s="12"/>
       <c r="H86" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="I86" s="12">
         <f t="shared" si="23"/>
@@ -19058,14 +19567,16 @@
       </c>
       <c r="J86" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K86" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="K86" s="12">
+        <v>0</v>
+      </c>
       <c r="L86" s="10"/>
       <c r="M86" s="12"/>
       <c r="N86" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="O86" s="12">
         <f t="shared" si="25"/>
@@ -19073,14 +19584,16 @@
       </c>
       <c r="P86" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q86" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="Q86" s="12">
+        <v>0</v>
+      </c>
       <c r="R86" s="10"/>
       <c r="S86" s="12"/>
       <c r="T86" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="U86" s="12">
         <f t="shared" si="17"/>
@@ -19088,38 +19601,44 @@
       </c>
       <c r="V86" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W86" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="W86" s="12">
+        <v>0</v>
+      </c>
       <c r="X86" s="10"/>
       <c r="Y86" s="12"/>
       <c r="Z86" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="AA86" s="12">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>8</v>
       </c>
       <c r="B87" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C87" s="10"/>
+      <c r="C87" s="10">
+        <v>173</v>
+      </c>
       <c r="D87" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E87" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="E87" s="12">
+        <v>0</v>
+      </c>
       <c r="F87" s="10"/>
       <c r="G87" s="12"/>
       <c r="H87" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="I87" s="12">
         <f t="shared" si="23"/>
@@ -19127,14 +19646,16 @@
       </c>
       <c r="J87" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K87" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="K87" s="12">
+        <v>0</v>
+      </c>
       <c r="L87" s="10"/>
       <c r="M87" s="12"/>
       <c r="N87" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="O87" s="12">
         <f t="shared" si="25"/>
@@ -19142,14 +19663,16 @@
       </c>
       <c r="P87" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q87" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="Q87" s="12">
+        <v>0</v>
+      </c>
       <c r="R87" s="10"/>
       <c r="S87" s="12"/>
       <c r="T87" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="U87" s="12">
         <f t="shared" si="17"/>
@@ -19157,38 +19680,44 @@
       </c>
       <c r="V87" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W87" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="W87" s="12">
+        <v>0</v>
+      </c>
       <c r="X87" s="10"/>
       <c r="Y87" s="12"/>
       <c r="Z87" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="AA87" s="12">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="19.5">
       <c r="A88" s="38">
         <v>8</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C88" s="12"/>
+        <v>90</v>
+      </c>
+      <c r="C88" s="10">
+        <v>173</v>
+      </c>
       <c r="D88" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E88" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="E88" s="12">
+        <v>0</v>
+      </c>
       <c r="F88" s="10"/>
       <c r="G88" s="12"/>
       <c r="H88" s="12">
         <f>IF((D88-E88)&lt;0,0,(D88-E88))</f>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="I88" s="12">
         <f>IF((E88-D88)&lt;0,0,(E88-D88))</f>
@@ -19196,14 +19725,16 @@
       </c>
       <c r="J88" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K88" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="K88" s="12">
+        <v>0</v>
+      </c>
       <c r="L88" s="10"/>
       <c r="M88" s="12"/>
       <c r="N88" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="O88" s="12">
         <f t="shared" si="25"/>
@@ -19211,14 +19742,16 @@
       </c>
       <c r="P88" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q88" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="Q88" s="12">
+        <v>0</v>
+      </c>
       <c r="R88" s="10"/>
       <c r="S88" s="12"/>
       <c r="T88" s="12">
         <f>IF((P88-Q88)&lt;0,0,(P88-Q88))</f>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="U88" s="12">
         <f>IF((Q88-P88)&lt;0,0,(Q88-P88))</f>
@@ -19226,38 +19759,44 @@
       </c>
       <c r="V88" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W88" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="W88" s="12">
+        <v>0</v>
+      </c>
       <c r="X88" s="10"/>
       <c r="Y88" s="12"/>
       <c r="Z88" s="12">
         <f>IF((V88-W88)&lt;0,0,(V88-W88))</f>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="AA88" s="12">
         <f>IF((W88-V88)&lt;0,0,(W88-V88))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>8</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C89" s="10"/>
+        <v>91</v>
+      </c>
+      <c r="C89" s="10">
+        <v>173</v>
+      </c>
       <c r="D89" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E89" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="E89" s="12">
+        <v>0</v>
+      </c>
       <c r="F89" s="10"/>
       <c r="G89" s="12"/>
       <c r="H89" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="I89" s="12">
         <f t="shared" si="23"/>
@@ -19265,14 +19804,16 @@
       </c>
       <c r="J89" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K89" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="K89" s="12">
+        <v>0</v>
+      </c>
       <c r="L89" s="10"/>
       <c r="M89" s="12"/>
       <c r="N89" s="12">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="O89" s="12">
         <f t="shared" si="25"/>
@@ -19280,14 +19821,16 @@
       </c>
       <c r="P89" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q89" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="Q89" s="12">
+        <v>0</v>
+      </c>
       <c r="R89" s="10"/>
       <c r="S89" s="12"/>
       <c r="T89" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="U89" s="12">
         <f t="shared" si="17"/>
@@ -19295,14 +19838,16 @@
       </c>
       <c r="V89" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W89" s="12"/>
+        <v>1384</v>
+      </c>
+      <c r="W89" s="12">
+        <v>0</v>
+      </c>
       <c r="X89" s="10"/>
       <c r="Y89" s="12"/>
       <c r="Z89" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="AA89" s="12">
         <f t="shared" si="19"/>
@@ -19317,17 +19862,21 @@
       <c r="B91" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C91" s="10"/>
+      <c r="C91" s="10">
+        <v>169</v>
+      </c>
       <c r="D91" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E91" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="E91" s="12">
+        <v>0</v>
+      </c>
       <c r="F91" s="10"/>
       <c r="G91" s="12"/>
       <c r="H91" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="I91" s="12">
         <f t="shared" si="23"/>
@@ -19335,14 +19884,16 @@
       </c>
       <c r="J91" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K91" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="K91" s="12">
+        <v>0</v>
+      </c>
       <c r="L91" s="10"/>
       <c r="M91" s="12"/>
       <c r="N91" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="O91" s="12">
         <f t="shared" si="21"/>
@@ -19350,14 +19901,16 @@
       </c>
       <c r="P91" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q91" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="Q91" s="12">
+        <v>0</v>
+      </c>
       <c r="R91" s="10"/>
       <c r="S91" s="12"/>
       <c r="T91" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="U91" s="12">
         <f t="shared" si="17"/>
@@ -19365,7 +19918,7 @@
       </c>
       <c r="V91" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="W91" s="12">
         <v>1280</v>
@@ -19373,14 +19926,16 @@
       <c r="X91" s="10">
         <v>2025</v>
       </c>
-      <c r="Y91" s="12"/>
+      <c r="Y91" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="Z91" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AA91" s="12">
         <f t="shared" si="19"/>
-        <v>1280</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:27" ht="19.5">
@@ -19390,10 +19945,12 @@
       <c r="B92" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C92" s="10"/>
+      <c r="C92" s="10">
+        <v>169</v>
+      </c>
       <c r="D92" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="E92" s="12">
         <v>306</v>
@@ -19402,19 +19959,19 @@
         <v>2025</v>
       </c>
       <c r="G92" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H92" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1046</v>
       </c>
       <c r="I92" s="12">
         <f t="shared" si="23"/>
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="J92" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="K92" s="12">
         <v>322</v>
@@ -19423,19 +19980,19 @@
         <v>2025</v>
       </c>
       <c r="M92" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="N92" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1030</v>
       </c>
       <c r="O92" s="12">
         <f t="shared" si="21"/>
-        <v>322</v>
+        <v>0</v>
       </c>
       <c r="P92" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="Q92" s="12">
         <v>225</v>
@@ -19444,19 +20001,19 @@
         <v>2025</v>
       </c>
       <c r="S92" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="T92" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1127</v>
       </c>
       <c r="U92" s="12">
         <f t="shared" si="17"/>
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="V92" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="W92" s="12">
         <v>315</v>
@@ -19465,15 +20022,15 @@
         <v>2025</v>
       </c>
       <c r="Y92" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z92" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1037</v>
       </c>
       <c r="AA92" s="12">
         <f t="shared" si="19"/>
-        <v>315</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:27" ht="19.5">
@@ -19483,10 +20040,12 @@
       <c r="B93" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C93" s="10"/>
+      <c r="C93" s="10">
+        <v>169</v>
+      </c>
       <c r="D93" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="E93" s="12">
         <v>1173</v>
@@ -19495,19 +20054,19 @@
         <v>2025</v>
       </c>
       <c r="G93" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H93" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="I93" s="12">
         <f t="shared" si="23"/>
-        <v>1173</v>
+        <v>0</v>
       </c>
       <c r="J93" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="K93" s="12">
         <v>760</v>
@@ -19516,19 +20075,19 @@
         <v>2025</v>
       </c>
       <c r="M93" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="N93" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>592</v>
       </c>
       <c r="O93" s="12">
         <f t="shared" si="21"/>
-        <v>760</v>
+        <v>0</v>
       </c>
       <c r="P93" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="Q93" s="12">
         <v>1270</v>
@@ -19537,19 +20096,19 @@
         <v>2025</v>
       </c>
       <c r="S93" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="T93" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="U93" s="12">
         <f t="shared" si="17"/>
-        <v>1270</v>
+        <v>0</v>
       </c>
       <c r="V93" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="W93" s="12">
         <v>755</v>
@@ -19558,15 +20117,15 @@
         <v>2025</v>
       </c>
       <c r="Y93" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z93" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>597</v>
       </c>
       <c r="AA93" s="12">
         <f t="shared" si="19"/>
-        <v>755</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:27" ht="19.5">
@@ -19576,17 +20135,21 @@
       <c r="B94" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C94" s="10"/>
+      <c r="C94" s="10">
+        <v>169</v>
+      </c>
       <c r="D94" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E94" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="E94" s="12">
+        <v>0</v>
+      </c>
       <c r="F94" s="10"/>
       <c r="G94" s="12"/>
       <c r="H94" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="I94" s="12">
         <f t="shared" si="23"/>
@@ -19594,14 +20157,16 @@
       </c>
       <c r="J94" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K94" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="K94" s="12">
+        <v>0</v>
+      </c>
       <c r="L94" s="10"/>
       <c r="M94" s="12"/>
       <c r="N94" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="O94" s="12">
         <f t="shared" si="21"/>
@@ -19609,7 +20174,7 @@
       </c>
       <c r="P94" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="Q94" s="12">
         <v>275</v>
@@ -19618,19 +20183,19 @@
         <v>2025</v>
       </c>
       <c r="S94" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="T94" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1077</v>
       </c>
       <c r="U94" s="12">
         <f t="shared" si="17"/>
-        <v>275</v>
+        <v>0</v>
       </c>
       <c r="V94" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="W94" s="12">
         <v>710</v>
@@ -19639,15 +20204,15 @@
         <v>2025</v>
       </c>
       <c r="Y94" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z94" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>642</v>
       </c>
       <c r="AA94" s="12">
         <f t="shared" si="19"/>
-        <v>710</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:27" ht="19.5">
@@ -19657,17 +20222,21 @@
       <c r="B95" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C95" s="10"/>
+      <c r="C95" s="10">
+        <v>169</v>
+      </c>
       <c r="D95" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E95" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="E95" s="12">
+        <v>0</v>
+      </c>
       <c r="F95" s="10"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="I95" s="12">
         <f t="shared" si="23"/>
@@ -19675,14 +20244,16 @@
       </c>
       <c r="J95" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K95" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="K95" s="12">
+        <v>0</v>
+      </c>
       <c r="L95" s="10"/>
       <c r="M95" s="12"/>
       <c r="N95" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="O95" s="12">
         <f t="shared" si="21"/>
@@ -19690,7 +20261,7 @@
       </c>
       <c r="P95" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="Q95" s="12">
         <v>565</v>
@@ -19699,19 +20270,19 @@
         <v>2025</v>
       </c>
       <c r="S95" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="T95" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>787</v>
       </c>
       <c r="U95" s="12">
         <f t="shared" si="17"/>
-        <v>565</v>
+        <v>0</v>
       </c>
       <c r="V95" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="W95" s="12">
         <v>230</v>
@@ -19720,15 +20291,15 @@
         <v>2025</v>
       </c>
       <c r="Y95" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z95" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1122</v>
       </c>
       <c r="AA95" s="12">
         <f t="shared" si="19"/>
-        <v>230</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:27" ht="19.5">
@@ -19738,17 +20309,21 @@
       <c r="B96" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C96" s="10"/>
+      <c r="C96" s="10">
+        <v>169</v>
+      </c>
       <c r="D96" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E96" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="E96" s="12">
+        <v>0</v>
+      </c>
       <c r="F96" s="10"/>
       <c r="G96" s="12"/>
       <c r="H96" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="I96" s="12">
         <f t="shared" si="23"/>
@@ -19756,14 +20331,16 @@
       </c>
       <c r="J96" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K96" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="K96" s="12">
+        <v>0</v>
+      </c>
       <c r="L96" s="10"/>
       <c r="M96" s="12"/>
       <c r="N96" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="O96" s="12">
         <f t="shared" si="21"/>
@@ -19771,7 +20348,7 @@
       </c>
       <c r="P96" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="Q96" s="12">
         <v>520</v>
@@ -19780,19 +20357,19 @@
         <v>2025</v>
       </c>
       <c r="S96" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="T96" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>832</v>
       </c>
       <c r="U96" s="12">
         <f t="shared" si="17"/>
-        <v>520</v>
+        <v>0</v>
       </c>
       <c r="V96" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="W96" s="12">
         <v>750</v>
@@ -19801,15 +20378,15 @@
         <v>2025</v>
       </c>
       <c r="Y96" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z96" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>602</v>
       </c>
       <c r="AA96" s="12">
         <f t="shared" si="19"/>
-        <v>750</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:27" ht="19.5">
@@ -19817,19 +20394,23 @@
         <v>9</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C97" s="10"/>
+        <v>88</v>
+      </c>
+      <c r="C97" s="10">
+        <v>169</v>
+      </c>
       <c r="D97" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E97" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="E97" s="12">
+        <v>0</v>
+      </c>
       <c r="F97" s="10"/>
       <c r="G97" s="12"/>
       <c r="H97" s="12">
         <f>IF((D97-E97)&lt;0,0,(D97-E97))</f>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="I97" s="12">
         <f>IF((E97-D97)&lt;0,0,(E97-D97))</f>
@@ -19837,14 +20418,16 @@
       </c>
       <c r="J97" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K97" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="K97" s="12">
+        <v>0</v>
+      </c>
       <c r="L97" s="10"/>
       <c r="M97" s="12"/>
       <c r="N97" s="12">
         <f t="shared" ref="N97:N101" si="26">IF((J97-K97)&lt;0,0,(J97-K97))</f>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="O97" s="12">
         <f t="shared" ref="O97:O101" si="27">IF((K97-J97)&lt;0,0,(K97-J97))</f>
@@ -19852,14 +20435,16 @@
       </c>
       <c r="P97" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q97" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="Q97" s="12">
+        <v>0</v>
+      </c>
       <c r="R97" s="10"/>
       <c r="S97" s="12"/>
       <c r="T97" s="12">
         <f>IF((P97-Q97)&lt;0,0,(P97-Q97))</f>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="U97" s="12">
         <f>IF((Q97-P97)&lt;0,0,(Q97-P97))</f>
@@ -19867,7 +20452,7 @@
       </c>
       <c r="V97" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="W97" s="12">
         <v>760</v>
@@ -19876,15 +20461,15 @@
         <v>2025</v>
       </c>
       <c r="Y97" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z97" s="12">
         <f>IF((V97-W97)&lt;0,0,(V97-W97))</f>
-        <v>0</v>
+        <v>592</v>
       </c>
       <c r="AA97" s="12">
         <f>IF((W97-V97)&lt;0,0,(W97-V97))</f>
-        <v>760</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:27" ht="19.5">
@@ -19892,19 +20477,23 @@
         <v>9</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C98" s="10"/>
+        <v>89</v>
+      </c>
+      <c r="C98" s="10">
+        <v>169</v>
+      </c>
       <c r="D98" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E98" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="E98" s="12">
+        <v>0</v>
+      </c>
       <c r="F98" s="10"/>
       <c r="G98" s="12"/>
       <c r="H98" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="I98" s="12">
         <f t="shared" si="23"/>
@@ -19912,14 +20501,16 @@
       </c>
       <c r="J98" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K98" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="K98" s="12">
+        <v>0</v>
+      </c>
       <c r="L98" s="10"/>
       <c r="M98" s="12"/>
       <c r="N98" s="12">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="O98" s="12">
         <f t="shared" si="27"/>
@@ -19927,14 +20518,16 @@
       </c>
       <c r="P98" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q98" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="Q98" s="12">
+        <v>0</v>
+      </c>
       <c r="R98" s="10"/>
       <c r="S98" s="12"/>
       <c r="T98" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="U98" s="12">
         <f t="shared" si="17"/>
@@ -19942,7 +20535,7 @@
       </c>
       <c r="V98" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="W98" s="12">
         <v>710</v>
@@ -19951,15 +20544,15 @@
         <v>2025</v>
       </c>
       <c r="Y98" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z98" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>642</v>
       </c>
       <c r="AA98" s="12">
         <f t="shared" si="19"/>
-        <v>710</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:27" ht="19.5">
@@ -19969,17 +20562,21 @@
       <c r="B99" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C99" s="10"/>
+      <c r="C99" s="10">
+        <v>169</v>
+      </c>
       <c r="D99" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E99" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="E99" s="12">
+        <v>0</v>
+      </c>
       <c r="F99" s="10"/>
       <c r="G99" s="12"/>
       <c r="H99" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="I99" s="12">
         <f t="shared" si="23"/>
@@ -19987,14 +20584,16 @@
       </c>
       <c r="J99" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K99" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="K99" s="12">
+        <v>0</v>
+      </c>
       <c r="L99" s="10"/>
       <c r="M99" s="12"/>
       <c r="N99" s="12">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="O99" s="12">
         <f t="shared" si="27"/>
@@ -20002,14 +20601,16 @@
       </c>
       <c r="P99" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q99" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="Q99" s="12">
+        <v>0</v>
+      </c>
       <c r="R99" s="10"/>
       <c r="S99" s="12"/>
       <c r="T99" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="U99" s="12">
         <f t="shared" si="17"/>
@@ -20017,14 +20618,16 @@
       </c>
       <c r="V99" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W99" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="W99" s="12">
+        <v>0</v>
+      </c>
       <c r="X99" s="10"/>
       <c r="Y99" s="12"/>
       <c r="Z99" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="AA99" s="12">
         <f t="shared" si="19"/>
@@ -20036,19 +20639,23 @@
         <v>9</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C100" s="10"/>
+        <v>90</v>
+      </c>
+      <c r="C100" s="10">
+        <v>169</v>
+      </c>
       <c r="D100" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E100" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="E100" s="12">
+        <v>0</v>
+      </c>
       <c r="F100" s="10"/>
       <c r="G100" s="12"/>
       <c r="H100" s="12">
         <f>IF((D100-E100)&lt;0,0,(D100-E100))</f>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="I100" s="12">
         <f>IF((E100-D100)&lt;0,0,(E100-D100))</f>
@@ -20056,14 +20663,16 @@
       </c>
       <c r="J100" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K100" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="K100" s="12">
+        <v>0</v>
+      </c>
       <c r="L100" s="10"/>
       <c r="M100" s="12"/>
       <c r="N100" s="12">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="O100" s="12">
         <f t="shared" si="27"/>
@@ -20071,7 +20680,7 @@
       </c>
       <c r="P100" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="Q100" s="12">
         <v>760</v>
@@ -20080,19 +20689,19 @@
         <v>2025</v>
       </c>
       <c r="S100" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="T100" s="12">
         <f>IF((P100-Q100)&lt;0,0,(P100-Q100))</f>
-        <v>0</v>
+        <v>592</v>
       </c>
       <c r="U100" s="12">
         <f>IF((Q100-P100)&lt;0,0,(Q100-P100))</f>
-        <v>760</v>
+        <v>0</v>
       </c>
       <c r="V100" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="W100" s="12">
         <v>425</v>
@@ -20101,15 +20710,15 @@
         <v>2025</v>
       </c>
       <c r="Y100" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z100" s="12">
         <f>IF((V100-W100)&lt;0,0,(V100-W100))</f>
-        <v>0</v>
+        <v>927</v>
       </c>
       <c r="AA100" s="12">
         <f>IF((W100-V100)&lt;0,0,(W100-V100))</f>
-        <v>425</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:27" ht="19.5">
@@ -20117,19 +20726,23 @@
         <v>9</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C101" s="10"/>
+        <v>91</v>
+      </c>
+      <c r="C101" s="10">
+        <v>169</v>
+      </c>
       <c r="D101" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E101" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="E101" s="12">
+        <v>0</v>
+      </c>
       <c r="F101" s="10"/>
       <c r="G101" s="12"/>
       <c r="H101" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="I101" s="12">
         <f t="shared" si="23"/>
@@ -20137,14 +20750,16 @@
       </c>
       <c r="J101" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K101" s="12"/>
+        <v>1352</v>
+      </c>
+      <c r="K101" s="12">
+        <v>0</v>
+      </c>
       <c r="L101" s="10"/>
       <c r="M101" s="12"/>
       <c r="N101" s="12">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="O101" s="12">
         <f t="shared" si="27"/>
@@ -20152,7 +20767,7 @@
       </c>
       <c r="P101" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="Q101" s="12">
         <v>135</v>
@@ -20161,19 +20776,19 @@
         <v>2025</v>
       </c>
       <c r="S101" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="T101" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1217</v>
       </c>
       <c r="U101" s="12">
         <f t="shared" si="17"/>
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="V101" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="W101" s="12">
         <v>375</v>
@@ -20182,15 +20797,15 @@
         <v>2025</v>
       </c>
       <c r="Y101" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z101" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>977</v>
       </c>
       <c r="AA101" s="12">
         <f t="shared" si="19"/>
-        <v>375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:27" s="7" customFormat="1"/>
@@ -20201,10 +20816,12 @@
       <c r="B103" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C103" s="10"/>
+      <c r="C103" s="10">
+        <v>130</v>
+      </c>
       <c r="D103" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="E103" s="12">
         <v>700</v>
@@ -20213,19 +20830,19 @@
         <v>2025</v>
       </c>
       <c r="G103" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H103" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="I103" s="12">
         <f t="shared" si="23"/>
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="J103" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="K103" s="12">
         <v>500</v>
@@ -20234,19 +20851,19 @@
         <v>2025</v>
       </c>
       <c r="M103" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="N103" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="O103" s="12">
         <f t="shared" si="21"/>
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="P103" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="Q103" s="12">
         <v>400</v>
@@ -20255,19 +20872,19 @@
         <v>2025</v>
       </c>
       <c r="S103" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="T103" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="U103" s="12">
         <f t="shared" si="17"/>
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="V103" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="W103" s="12">
         <v>300</v>
@@ -20276,15 +20893,15 @@
         <v>2025</v>
       </c>
       <c r="Y103" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z103" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>740</v>
       </c>
       <c r="AA103" s="12">
         <f t="shared" si="19"/>
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:27" ht="19.5">
@@ -20294,10 +20911,12 @@
       <c r="B104" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C104" s="10"/>
+      <c r="C104" s="10">
+        <v>130</v>
+      </c>
       <c r="D104" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="E104" s="12">
         <v>700</v>
@@ -20306,26 +20925,28 @@
         <v>2025</v>
       </c>
       <c r="G104" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H104" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="I104" s="12">
         <f t="shared" si="23"/>
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="J104" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K104" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="K104" s="12">
+        <v>0</v>
+      </c>
       <c r="L104" s="10"/>
       <c r="M104" s="12"/>
       <c r="N104" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="O104" s="12">
         <f t="shared" si="21"/>
@@ -20333,7 +20954,7 @@
       </c>
       <c r="P104" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="Q104" s="12">
         <v>400</v>
@@ -20342,19 +20963,19 @@
         <v>2025</v>
       </c>
       <c r="S104" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="T104" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="U104" s="12">
         <f t="shared" si="17"/>
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="V104" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="W104" s="12">
         <v>700</v>
@@ -20363,15 +20984,15 @@
         <v>2025</v>
       </c>
       <c r="Y104" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z104" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="AA104" s="12">
         <f t="shared" si="19"/>
-        <v>700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:27" ht="19.5">
@@ -20381,10 +21002,12 @@
       <c r="B105" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C105" s="10"/>
+      <c r="C105" s="10">
+        <v>130</v>
+      </c>
       <c r="D105" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="E105" s="12">
         <v>1000</v>
@@ -20393,19 +21016,19 @@
         <v>2025</v>
       </c>
       <c r="G105" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H105" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I105" s="12">
         <f t="shared" si="23"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J105" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="K105" s="12">
         <v>500</v>
@@ -20414,19 +21037,19 @@
         <v>2025</v>
       </c>
       <c r="M105" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="N105" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="O105" s="12">
         <f t="shared" si="21"/>
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="P105" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="Q105" s="12">
         <v>600</v>
@@ -20435,19 +21058,19 @@
         <v>2025</v>
       </c>
       <c r="S105" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="T105" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="U105" s="12">
         <f t="shared" si="17"/>
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="V105" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="W105" s="12">
         <v>400</v>
@@ -20456,15 +21079,15 @@
         <v>2025</v>
       </c>
       <c r="Y105" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z105" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="AA105" s="12">
         <f t="shared" si="19"/>
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:27" ht="19.5">
@@ -20474,17 +21097,21 @@
       <c r="B106" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C106" s="10"/>
+      <c r="C106" s="10">
+        <v>130</v>
+      </c>
       <c r="D106" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E106" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="E106" s="12">
+        <v>0</v>
+      </c>
       <c r="F106" s="10"/>
       <c r="G106" s="12"/>
       <c r="H106" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="I106" s="12">
         <f t="shared" si="23"/>
@@ -20492,14 +21119,16 @@
       </c>
       <c r="J106" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K106" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="K106" s="12">
+        <v>0</v>
+      </c>
       <c r="L106" s="10"/>
       <c r="M106" s="12"/>
       <c r="N106" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="O106" s="12">
         <f t="shared" si="21"/>
@@ -20507,7 +21136,7 @@
       </c>
       <c r="P106" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="Q106" s="12">
         <v>650</v>
@@ -20516,19 +21145,19 @@
         <v>2025</v>
       </c>
       <c r="S106" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="T106" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="U106" s="12">
         <f t="shared" si="17"/>
-        <v>650</v>
+        <v>0</v>
       </c>
       <c r="V106" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="W106" s="12">
         <v>400</v>
@@ -20537,15 +21166,15 @@
         <v>2025</v>
       </c>
       <c r="Y106" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z106" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="AA106" s="12">
         <f t="shared" si="19"/>
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:27" ht="19.5">
@@ -20555,17 +21184,21 @@
       <c r="B107" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C107" s="10"/>
+      <c r="C107" s="10">
+        <v>130</v>
+      </c>
       <c r="D107" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E107" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="E107" s="12">
+        <v>0</v>
+      </c>
       <c r="F107" s="10"/>
       <c r="G107" s="12"/>
       <c r="H107" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="I107" s="12">
         <f t="shared" si="23"/>
@@ -20573,14 +21206,16 @@
       </c>
       <c r="J107" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K107" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="K107" s="12">
+        <v>0</v>
+      </c>
       <c r="L107" s="10"/>
       <c r="M107" s="12"/>
       <c r="N107" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="O107" s="12">
         <f t="shared" si="21"/>
@@ -20588,7 +21223,7 @@
       </c>
       <c r="P107" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="Q107" s="12">
         <v>250</v>
@@ -20597,19 +21232,19 @@
         <v>2025</v>
       </c>
       <c r="S107" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="T107" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>790</v>
       </c>
       <c r="U107" s="12">
         <f t="shared" si="17"/>
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="V107" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="W107" s="12">
         <v>400</v>
@@ -20618,15 +21253,15 @@
         <v>2025</v>
       </c>
       <c r="Y107" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z107" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="AA107" s="12">
         <f t="shared" si="19"/>
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:27" ht="19.5">
@@ -20636,17 +21271,21 @@
       <c r="B108" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C108" s="10"/>
+      <c r="C108" s="10">
+        <v>130</v>
+      </c>
       <c r="D108" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E108" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="E108" s="12">
+        <v>0</v>
+      </c>
       <c r="F108" s="10"/>
       <c r="G108" s="12"/>
       <c r="H108" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="I108" s="12">
         <f t="shared" si="23"/>
@@ -20654,14 +21293,16 @@
       </c>
       <c r="J108" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K108" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="K108" s="12">
+        <v>0</v>
+      </c>
       <c r="L108" s="10"/>
       <c r="M108" s="12"/>
       <c r="N108" s="12">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="O108" s="12">
         <f t="shared" si="21"/>
@@ -20669,7 +21310,7 @@
       </c>
       <c r="P108" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="Q108" s="12">
         <v>400</v>
@@ -20678,19 +21319,19 @@
         <v>2025</v>
       </c>
       <c r="S108" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="T108" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="U108" s="12">
         <f t="shared" si="17"/>
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="V108" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="W108" s="12">
         <v>600</v>
@@ -20699,15 +21340,15 @@
         <v>2025</v>
       </c>
       <c r="Y108" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z108" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="AA108" s="12">
         <f t="shared" si="19"/>
-        <v>600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:27" ht="19.5">
@@ -20715,19 +21356,23 @@
         <v>10</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C109" s="10"/>
+        <v>88</v>
+      </c>
+      <c r="C109" s="10">
+        <v>130</v>
+      </c>
       <c r="D109" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E109" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="E109" s="12">
+        <v>0</v>
+      </c>
       <c r="F109" s="10"/>
       <c r="G109" s="12"/>
       <c r="H109" s="12">
         <f>IF((D109-E109)&lt;0,0,(D109-E109))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="I109" s="12">
         <f>IF((E109-D109)&lt;0,0,(E109-D109))</f>
@@ -20735,14 +21380,16 @@
       </c>
       <c r="J109" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K109" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="K109" s="12">
+        <v>0</v>
+      </c>
       <c r="L109" s="10"/>
       <c r="M109" s="12"/>
       <c r="N109" s="12">
         <f t="shared" ref="N109:N113" si="28">IF((J109-K109)&lt;0,0,(J109-K109))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="O109" s="12">
         <f t="shared" ref="O109:O113" si="29">IF((K109-J109)&lt;0,0,(K109-J109))</f>
@@ -20750,14 +21397,16 @@
       </c>
       <c r="P109" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q109" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="Q109" s="12">
+        <v>0</v>
+      </c>
       <c r="R109" s="10"/>
       <c r="S109" s="12"/>
       <c r="T109" s="12">
         <f>IF((P109-Q109)&lt;0,0,(P109-Q109))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="U109" s="12">
         <f>IF((Q109-P109)&lt;0,0,(Q109-P109))</f>
@@ -20765,7 +21414,7 @@
       </c>
       <c r="V109" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="W109" s="12">
         <v>200</v>
@@ -20774,15 +21423,15 @@
         <v>2025</v>
       </c>
       <c r="Y109" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z109" s="12">
         <f>IF((V109-W109)&lt;0,0,(V109-W109))</f>
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="AA109" s="12">
         <f>IF((W109-V109)&lt;0,0,(W109-V109))</f>
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:27" ht="19.5">
@@ -20790,19 +21439,23 @@
         <v>10</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C110" s="10"/>
+        <v>89</v>
+      </c>
+      <c r="C110" s="10">
+        <v>130</v>
+      </c>
       <c r="D110" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E110" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="E110" s="12">
+        <v>0</v>
+      </c>
       <c r="F110" s="10"/>
       <c r="G110" s="12"/>
       <c r="H110" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="I110" s="12">
         <f t="shared" si="23"/>
@@ -20810,14 +21463,16 @@
       </c>
       <c r="J110" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K110" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="K110" s="12">
+        <v>0</v>
+      </c>
       <c r="L110" s="10"/>
       <c r="M110" s="12"/>
       <c r="N110" s="12">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="O110" s="12">
         <f t="shared" si="29"/>
@@ -20825,7 +21480,7 @@
       </c>
       <c r="P110" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="Q110" s="12">
         <v>300</v>
@@ -20834,19 +21489,19 @@
         <v>2025</v>
       </c>
       <c r="S110" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="T110" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>740</v>
       </c>
       <c r="U110" s="12">
         <f t="shared" si="17"/>
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="V110" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="W110" s="12">
         <v>400</v>
@@ -20855,35 +21510,39 @@
         <v>2025</v>
       </c>
       <c r="Y110" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z110" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="AA110" s="12">
         <f t="shared" si="19"/>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="111" spans="1:27" ht="19.149999999999999">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:27" ht="19.5">
       <c r="A111" s="10">
         <v>10</v>
       </c>
       <c r="B111" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C111" s="10"/>
+      <c r="C111" s="10">
+        <v>130</v>
+      </c>
       <c r="D111" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E111" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="E111" s="12">
+        <v>0</v>
+      </c>
       <c r="F111" s="10"/>
       <c r="G111" s="12"/>
       <c r="H111" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="I111" s="12">
         <f t="shared" si="23"/>
@@ -20891,14 +21550,16 @@
       </c>
       <c r="J111" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K111" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="K111" s="12">
+        <v>0</v>
+      </c>
       <c r="L111" s="10"/>
       <c r="M111" s="12"/>
       <c r="N111" s="12">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="O111" s="12">
         <f t="shared" si="29"/>
@@ -20906,14 +21567,16 @@
       </c>
       <c r="P111" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="Q111" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="Q111" s="12">
+        <v>0</v>
+      </c>
       <c r="R111" s="10"/>
       <c r="S111" s="12"/>
       <c r="T111" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="U111" s="12">
         <f t="shared" si="17"/>
@@ -20921,14 +21584,16 @@
       </c>
       <c r="V111" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W111" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="W111" s="12">
+        <v>0</v>
+      </c>
       <c r="X111" s="10"/>
       <c r="Y111" s="12"/>
       <c r="Z111" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="AA111" s="12">
         <f t="shared" si="19"/>
@@ -20940,19 +21605,23 @@
         <v>10</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C112" s="10"/>
+        <v>90</v>
+      </c>
+      <c r="C112" s="10">
+        <v>130</v>
+      </c>
       <c r="D112" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E112" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="E112" s="12">
+        <v>0</v>
+      </c>
       <c r="F112" s="10"/>
       <c r="G112" s="12"/>
       <c r="H112" s="12">
         <f>IF((D112-E112)&lt;0,0,(D112-E112))</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="I112" s="12">
         <f>IF((E112-D112)&lt;0,0,(E112-D112))</f>
@@ -20960,14 +21629,16 @@
       </c>
       <c r="J112" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K112" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="K112" s="12">
+        <v>0</v>
+      </c>
       <c r="L112" s="10"/>
       <c r="M112" s="12"/>
       <c r="N112" s="12">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="O112" s="12">
         <f t="shared" si="29"/>
@@ -20975,7 +21646,7 @@
       </c>
       <c r="P112" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="Q112" s="12">
         <v>200</v>
@@ -20984,19 +21655,19 @@
         <v>2025</v>
       </c>
       <c r="S112" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="T112" s="12">
         <f>IF((P112-Q112)&lt;0,0,(P112-Q112))</f>
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="U112" s="12">
         <f>IF((Q112-P112)&lt;0,0,(Q112-P112))</f>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="V112" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="W112" s="12">
         <v>100</v>
@@ -21005,15 +21676,15 @@
         <v>2025</v>
       </c>
       <c r="Y112" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z112" s="12">
         <f>IF((V112-W112)&lt;0,0,(V112-W112))</f>
-        <v>0</v>
+        <v>940</v>
       </c>
       <c r="AA112" s="12">
         <f>IF((W112-V112)&lt;0,0,(W112-V112))</f>
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:28" ht="19.5">
@@ -21021,19 +21692,23 @@
         <v>10</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C113" s="10"/>
+        <v>91</v>
+      </c>
+      <c r="C113" s="10">
+        <v>130</v>
+      </c>
       <c r="D113" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E113" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="E113" s="12">
+        <v>0</v>
+      </c>
       <c r="F113" s="10"/>
       <c r="G113" s="12"/>
       <c r="H113" s="12">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="I113" s="12">
         <f t="shared" si="23"/>
@@ -21041,14 +21716,16 @@
       </c>
       <c r="J113" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K113" s="12"/>
+        <v>1040</v>
+      </c>
+      <c r="K113" s="12">
+        <v>0</v>
+      </c>
       <c r="L113" s="10"/>
       <c r="M113" s="12"/>
       <c r="N113" s="12">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="O113" s="12">
         <f t="shared" si="29"/>
@@ -21056,7 +21733,7 @@
       </c>
       <c r="P113" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="Q113" s="12">
         <v>200</v>
@@ -21065,19 +21742,19 @@
         <v>2025</v>
       </c>
       <c r="S113" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="T113" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="U113" s="12">
         <f t="shared" si="17"/>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="V113" s="12">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="W113" s="12">
         <v>300</v>
@@ -21086,15 +21763,15 @@
         <v>2025</v>
       </c>
       <c r="Y113" s="12" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Z113" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>740</v>
       </c>
       <c r="AA113" s="12">
         <f t="shared" si="19"/>
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:28" s="7" customFormat="1"/>
@@ -21581,7 +22258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.450000000000003">
+    <row r="122" spans="1:28" ht="38.25">
       <c r="A122" s="1" t="s">
         <v>24</v>
       </c>
@@ -22161,189 +22838,9 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
+    <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C115:C122 C67:C77 C79:C89 C91:C101 C103:C113" name="Textbooks"/>
     <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113" name="LAS"/>
     <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 S55:S65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 G91:G101 M91:M101 S91:S101 G103:G113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122 Y91:Y101 Y103:Y113" name="SOURCE"/>
   </protectedRanges>
@@ -22358,8 +22855,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 M115:M122 S91:S101 M91:M101 G91:G101 G103:G113 Y91:Y101 S103:S113 M103:M113 Y103:Y113" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113 X115:X122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 F67:F77 F79:F89 F91:F101 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
